--- a/TachPP_BL_ChiTiet.xlsx
+++ b/TachPP_BL_ChiTiet.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Times New Roman"/>
       <family val="2"/>
@@ -53,8 +53,26 @@
       <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="001A5276"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
+      <color rgb="007B3F00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +89,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD580"/>
       </patternFill>
     </fill>
   </fills>
@@ -240,7 +263,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -363,6 +386,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -763,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P312"/>
+  <dimension ref="A1:Q312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6"/>
   <cols>
     <col width="15.796875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -839,6 +886,11 @@
           <t>Trung/Hạ thế</t>
         </is>
       </c>
+      <c r="Q1" s="37" t="inlineStr">
+        <is>
+          <t>Loại giao dịch</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="14.4" customFormat="1" customHeight="1" s="20">
       <c r="A2" s="38" t="n"/>
@@ -893,6 +945,11 @@
           <t>PHÂN LOẠI</t>
         </is>
       </c>
+      <c r="Q2" s="25" t="inlineStr">
+        <is>
+          <t>XUẤT / THU HỒI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -953,6 +1010,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q3" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -1013,6 +1075,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q4" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -1073,6 +1140,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q5" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -1133,6 +1205,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q6" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -1193,6 +1270,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q7" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -1253,6 +1335,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q8" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -1313,6 +1400,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q9" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1373,6 +1465,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q10" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1433,6 +1530,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q11" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -1493,6 +1595,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q12" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1553,6 +1660,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q13" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -1613,6 +1725,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q14" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -1673,6 +1790,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q15" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -1733,6 +1855,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q16" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -1793,6 +1920,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q17" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -1853,6 +1985,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q18" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -1913,6 +2050,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q19" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -1973,6 +2115,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q20" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2033,6 +2180,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q21" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2093,6 +2245,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q22" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2153,6 +2310,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q23" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2213,6 +2375,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q24" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -2273,6 +2440,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q25" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -2333,6 +2505,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q26" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -2393,6 +2570,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q27" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -2453,6 +2635,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q28" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -2513,6 +2700,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q29" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -2573,6 +2765,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q30" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -2633,6 +2830,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q31" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -2693,6 +2895,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q32" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -2753,6 +2960,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q33" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -2813,6 +3025,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q34" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -2873,6 +3090,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q35" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -2933,6 +3155,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q36" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -2993,6 +3220,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q37" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -3053,6 +3285,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q38" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -3113,6 +3350,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q39" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -3173,6 +3415,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q40" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -3233,6 +3480,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q41" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -3293,6 +3545,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q42" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
@@ -3353,6 +3610,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q43" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
@@ -3413,64 +3675,74 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q44" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>3.56.60.056.VIE.00.000</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp TU 24kV 22000/√3/110/√3V-15VA CCX 0,5 epoxy chân không</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
+      <c r="C45" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D45" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F45" s="4" t="n">
+      <c r="E45" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F45" s="49" t="n">
         <v>46063</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="48" t="inlineStr">
         <is>
           <t>01.VH6.11.0001</t>
         </is>
       </c>
-      <c r="H45" s="6" t="n"/>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="H45" s="48" t="n"/>
+      <c r="I45" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập TU,  phục vụ SCL 2026 theo PGH:03.VH6.41.0004(02/02/2026)</t>
         </is>
       </c>
-      <c r="J45" s="43" t="n">
+      <c r="J45" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K45" s="43" t="n">
+      <c r="K45" s="50" t="n">
         <v>9892914.33</v>
       </c>
-      <c r="L45" s="43" t="n">
+      <c r="L45" s="50" t="n">
         <v>29678743</v>
       </c>
-      <c r="M45" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="45" t="inlineStr">
+      <c r="M45" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q45" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -3533,6 +3805,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q46" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -3593,6 +3870,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q47" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -3653,6 +3935,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q48" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -3713,6 +4000,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q49" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -3773,6 +4065,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q50" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -3833,6 +4130,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q51" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -3893,6 +4195,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q52" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -3953,6 +4260,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q53" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -4013,6 +4325,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q54" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -4073,6 +4390,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q55" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -4133,6 +4455,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q56" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -4193,6 +4520,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q57" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -4253,6 +4585,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q58" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -4313,6 +4650,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q59" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -4373,6 +4715,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q60" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -4433,6 +4780,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q61" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -4493,6 +4845,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q62" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -4553,6 +4910,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q63" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -4613,6 +4975,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q64" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -4673,6 +5040,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q65" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -4733,6 +5105,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q66" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -4793,6 +5170,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q67" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -4853,6 +5235,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q68" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -4913,6 +5300,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q69" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -4973,6 +5365,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q70" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -5033,6 +5430,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q71" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -5093,6 +5495,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q72" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -5153,6 +5560,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q73" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
@@ -5213,6 +5625,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q74" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -5273,6 +5690,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q75" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -5333,6 +5755,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q76" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
@@ -5393,6 +5820,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q77" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
@@ -5453,6 +5885,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q78" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
@@ -5513,6 +5950,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q79" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -5573,6 +6015,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q80" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
@@ -5633,6 +6080,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q81" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -5693,6 +6145,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q82" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -5753,6 +6210,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q83" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
@@ -5813,6 +6275,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q84" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -5873,6 +6340,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q85" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
@@ -5933,6 +6405,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q86" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -5993,244 +6470,269 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q87" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="A88" s="47" t="inlineStr">
         <is>
           <t>3.53.65.160.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B88" s="10" t="inlineStr">
+      <c r="B88" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 250-500/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="n">
+      <c r="C88" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D88" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="E88" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F88" s="4" t="n">
+      <c r="E88" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F88" s="49" t="n">
         <v>46105</v>
       </c>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="G88" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H88" s="6" t="n"/>
-      <c r="I88" s="9" t="inlineStr">
+      <c r="H88" s="48" t="n"/>
+      <c r="I88" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J88" s="43" t="n">
+      <c r="J88" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K88" s="43" t="n">
+      <c r="K88" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L88" s="43" t="n">
+      <c r="L88" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="M88" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" s="45" t="inlineStr">
+      <c r="M88" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q88" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="A89" s="47" t="inlineStr">
         <is>
           <t>3.53.65.145.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B89" s="10" t="inlineStr">
+      <c r="B89" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 20-40/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="n">
+      <c r="C89" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D89" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="E89" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F89" s="4" t="n">
+      <c r="E89" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F89" s="49" t="n">
         <v>46105</v>
       </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G89" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H89" s="6" t="n"/>
-      <c r="I89" s="9" t="inlineStr">
+      <c r="H89" s="48" t="n"/>
+      <c r="I89" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J89" s="43" t="n">
+      <c r="J89" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K89" s="43" t="n">
+      <c r="K89" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L89" s="43" t="n">
+      <c r="L89" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M89" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" s="45" t="inlineStr">
+      <c r="M89" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q89" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
+      <c r="A90" s="47" t="inlineStr">
         <is>
           <t>3.53.65.147.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B90" s="10" t="inlineStr">
+      <c r="B90" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 30-60/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="n">
+      <c r="C90" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D90" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="E90" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F90" s="4" t="n">
+      <c r="E90" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F90" s="49" t="n">
         <v>46105</v>
       </c>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="G90" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H90" s="6" t="n"/>
-      <c r="I90" s="9" t="inlineStr">
+      <c r="H90" s="48" t="n"/>
+      <c r="I90" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J90" s="43" t="n">
+      <c r="J90" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K90" s="43" t="n">
+      <c r="K90" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L90" s="43" t="n">
+      <c r="L90" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M90" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" s="45" t="inlineStr">
+      <c r="M90" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q90" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="10" t="inlineStr">
+      <c r="A91" s="47" t="inlineStr">
         <is>
           <t>3.53.65.025.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B91" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 25-50/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="n">
+      <c r="C91" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D91" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="E91" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F91" s="4" t="n">
+      <c r="E91" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F91" s="49" t="n">
         <v>46105</v>
       </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G91" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H91" s="6" t="n"/>
-      <c r="I91" s="9" t="inlineStr">
+      <c r="H91" s="48" t="n"/>
+      <c r="I91" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J91" s="43" t="n">
+      <c r="J91" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K91" s="43" t="n">
+      <c r="K91" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L91" s="43" t="n">
+      <c r="L91" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="M91" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" s="45" t="inlineStr">
+      <c r="M91" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q91" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -6293,6 +6795,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q92" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -6353,6 +6860,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q93" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
@@ -6413,6 +6925,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q94" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
@@ -6473,6 +6990,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q95" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
@@ -6533,6 +7055,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q96" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
@@ -6593,6 +7120,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q97" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
@@ -6653,64 +7185,74 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q98" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="10" t="inlineStr">
+      <c r="A99" s="47" t="inlineStr">
         <is>
           <t>3.53.65.145.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B99" s="10" t="inlineStr">
+      <c r="B99" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 20-40/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="n">
+      <c r="C99" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D99" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="E99" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F99" s="4" t="n">
+      <c r="E99" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F99" s="49" t="n">
         <v>46107</v>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G99" s="48" t="inlineStr">
         <is>
           <t>01.VH4.11.0039</t>
         </is>
       </c>
-      <c r="H99" s="6" t="n"/>
-      <c r="I99" s="9" t="inlineStr">
+      <c r="H99" s="48" t="n"/>
+      <c r="I99" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT thay SCL</t>
         </is>
       </c>
-      <c r="J99" s="43" t="n">
+      <c r="J99" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K99" s="43" t="n">
+      <c r="K99" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L99" s="43" t="n">
+      <c r="L99" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M99" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="45" t="inlineStr">
+      <c r="M99" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q99" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -6773,6 +7315,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q100" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
@@ -6833,6 +7380,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q101" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
@@ -6893,6 +7445,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q102" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
@@ -6953,6 +7510,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q103" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
@@ -7013,6 +7575,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q104" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
@@ -7073,6 +7640,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q105" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -7133,6 +7705,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q106" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
@@ -7193,6 +7770,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q107" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
@@ -7253,6 +7835,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q108" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
@@ -7313,6 +7900,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q109" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
@@ -7373,6 +7965,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q110" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
@@ -7433,6 +8030,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q111" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
@@ -7493,6 +8095,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q112" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
@@ -7553,6 +8160,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q113" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
@@ -7613,6 +8225,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q114" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
@@ -7673,6 +8290,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q115" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
@@ -7733,6 +8355,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q116" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
@@ -7793,6 +8420,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q117" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
@@ -7853,6 +8485,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q118" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
@@ -7913,6 +8550,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q119" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
@@ -7973,6 +8615,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q120" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
@@ -8033,6 +8680,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q121" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
@@ -8093,6 +8745,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q122" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
@@ -8153,6 +8810,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q123" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
@@ -8213,6 +8875,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q124" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
@@ -8273,6 +8940,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q125" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
@@ -8333,6 +9005,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q126" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
@@ -8393,6 +9070,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q127" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
@@ -8453,6 +9135,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q128" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
@@ -8513,6 +9200,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q129" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
@@ -8573,424 +9265,464 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q130" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="10" t="inlineStr">
+      <c r="A131" s="47" t="inlineStr">
         <is>
           <t>3.53.65.025.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B131" s="10" t="inlineStr">
+      <c r="B131" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 25-50/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="n">
+      <c r="C131" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D131" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E131" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F131" s="4" t="n">
+      <c r="E131" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F131" s="49" t="n">
         <v>46122</v>
       </c>
-      <c r="G131" s="5" t="inlineStr">
+      <c r="G131" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H131" s="6" t="n"/>
-      <c r="I131" s="9" t="inlineStr">
+      <c r="H131" s="48" t="n"/>
+      <c r="I131" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J131" s="43" t="n">
+      <c r="J131" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K131" s="43" t="n">
+      <c r="K131" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L131" s="43" t="n">
+      <c r="L131" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="M131" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" s="45" t="inlineStr">
+      <c r="M131" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q131" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="10" t="inlineStr">
+      <c r="A132" s="47" t="inlineStr">
         <is>
           <t>3.53.65.160.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B132" s="10" t="inlineStr">
+      <c r="B132" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 250-500/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="n">
+      <c r="C132" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D132" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E132" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F132" s="4" t="n">
+      <c r="E132" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F132" s="49" t="n">
         <v>46122</v>
       </c>
-      <c r="G132" s="5" t="inlineStr">
+      <c r="G132" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H132" s="6" t="n"/>
-      <c r="I132" s="9" t="inlineStr">
+      <c r="H132" s="48" t="n"/>
+      <c r="I132" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J132" s="43" t="n">
+      <c r="J132" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K132" s="43" t="n">
+      <c r="K132" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L132" s="43" t="n">
+      <c r="L132" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M132" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" s="45" t="inlineStr">
+      <c r="M132" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q132" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="10" t="inlineStr">
+      <c r="A133" s="47" t="inlineStr">
         <is>
           <t>3.53.65.145.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B133" s="10" t="inlineStr">
+      <c r="B133" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 20-40/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="n">
+      <c r="C133" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D133" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E133" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F133" s="4" t="n">
+      <c r="E133" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F133" s="49" t="n">
         <v>46122</v>
       </c>
-      <c r="G133" s="5" t="inlineStr">
+      <c r="G133" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H133" s="6" t="n"/>
-      <c r="I133" s="9" t="inlineStr">
+      <c r="H133" s="48" t="n"/>
+      <c r="I133" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J133" s="43" t="n">
+      <c r="J133" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="K133" s="43" t="n">
+      <c r="K133" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L133" s="43" t="n">
+      <c r="L133" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="M133" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" s="45" t="inlineStr">
+      <c r="M133" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q133" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="10" t="inlineStr">
+      <c r="A134" s="47" t="inlineStr">
         <is>
           <t>3.53.65.013.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B134" s="10" t="inlineStr">
+      <c r="B134" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 10-20/5A</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="n">
+      <c r="C134" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D134" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E134" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F134" s="4" t="n">
+      <c r="E134" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F134" s="49" t="n">
         <v>46122</v>
       </c>
-      <c r="G134" s="5" t="inlineStr">
+      <c r="G134" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H134" s="6" t="n"/>
-      <c r="I134" s="9" t="inlineStr">
+      <c r="H134" s="48" t="n"/>
+      <c r="I134" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J134" s="43" t="n">
+      <c r="J134" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K134" s="43" t="n">
+      <c r="K134" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L134" s="43" t="n">
+      <c r="L134" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="M134" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" s="45" t="inlineStr">
+      <c r="M134" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q134" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="10" t="inlineStr">
+      <c r="A135" s="47" t="inlineStr">
         <is>
           <t>3.53.65.015.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B135" s="10" t="inlineStr">
+      <c r="B135" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 15-30/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="n">
+      <c r="C135" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D135" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E135" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F135" s="4" t="n">
+      <c r="E135" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F135" s="49" t="n">
         <v>46122</v>
       </c>
-      <c r="G135" s="5" t="inlineStr">
+      <c r="G135" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H135" s="6" t="n"/>
-      <c r="I135" s="9" t="inlineStr">
+      <c r="H135" s="48" t="n"/>
+      <c r="I135" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J135" s="43" t="n">
+      <c r="J135" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K135" s="43" t="n">
+      <c r="K135" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L135" s="43" t="n">
+      <c r="L135" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M135" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" s="45" t="inlineStr">
+      <c r="M135" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q135" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="10" t="inlineStr">
+      <c r="A136" s="47" t="inlineStr">
         <is>
           <t>3.53.65.148.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B136" s="10" t="inlineStr">
+      <c r="B136" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 50-100/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="n">
+      <c r="C136" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D136" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E136" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F136" s="4" t="n">
+      <c r="E136" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F136" s="49" t="n">
         <v>46122</v>
       </c>
-      <c r="G136" s="5" t="inlineStr">
+      <c r="G136" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H136" s="6" t="n"/>
-      <c r="I136" s="9" t="inlineStr">
+      <c r="H136" s="48" t="n"/>
+      <c r="I136" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J136" s="43" t="n">
+      <c r="J136" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K136" s="43" t="n">
+      <c r="K136" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L136" s="43" t="n">
+      <c r="L136" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M136" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" s="45" t="inlineStr">
+      <c r="M136" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q136" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="10" t="inlineStr">
+      <c r="A137" s="47" t="inlineStr">
         <is>
           <t>3.56.60.056.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B137" s="10" t="inlineStr">
+      <c r="B137" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp TU 24kV 22000/√3/110/√3V-15VA CCX 0,5 epoxy chân không</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n">
+      <c r="C137" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D137" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E137" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F137" s="4" t="n">
+      <c r="E137" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F137" s="49" t="n">
         <v>46122</v>
       </c>
-      <c r="G137" s="5" t="inlineStr">
+      <c r="G137" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H137" s="6" t="n"/>
-      <c r="I137" s="9" t="inlineStr">
+      <c r="H137" s="48" t="n"/>
+      <c r="I137" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J137" s="43" t="n">
+      <c r="J137" s="50" t="n">
         <v>9</v>
       </c>
-      <c r="K137" s="43" t="n">
+      <c r="K137" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L137" s="43" t="n">
+      <c r="L137" s="50" t="n">
         <v>9</v>
       </c>
-      <c r="M137" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" s="45" t="inlineStr">
+      <c r="M137" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q137" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -9053,6 +9785,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q138" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
@@ -9113,6 +9850,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q139" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
@@ -9173,6 +9915,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q140" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
@@ -9233,6 +9980,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q141" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
@@ -9293,6 +10045,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q142" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
@@ -9353,6 +10110,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q143" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
@@ -9413,6 +10175,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q144" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
@@ -9473,6 +10240,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q145" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
@@ -9533,64 +10305,74 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q146" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="10" t="inlineStr">
+      <c r="A147" s="47" t="inlineStr">
         <is>
           <t>3.42.80.118.VIE.00.000</t>
         </is>
       </c>
-      <c r="B147" s="10" t="inlineStr">
+      <c r="B147" s="47" t="inlineStr">
         <is>
           <t>SPC - Chống sét van (LA) 18kV  Polymer kèm phụ kiện ( Dòng rò 31 mm/kV )</t>
         </is>
       </c>
-      <c r="C147" s="3" t="inlineStr">
+      <c r="C147" s="48" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D147" s="2" t="n">
+      <c r="D147" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E147" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F147" s="4" t="n">
+      <c r="E147" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F147" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G147" s="5" t="inlineStr">
+      <c r="G147" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0029</t>
         </is>
       </c>
-      <c r="H147" s="6" t="n"/>
-      <c r="I147" s="9" t="inlineStr">
+      <c r="H147" s="48" t="n"/>
+      <c r="I147" s="47" t="inlineStr">
         <is>
           <t>24017 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J147" s="43" t="n">
+      <c r="J147" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="K147" s="43" t="n">
+      <c r="K147" s="50" t="n">
         <v>1148800</v>
       </c>
-      <c r="L147" s="43" t="n">
+      <c r="L147" s="50" t="n">
         <v>5744000</v>
       </c>
-      <c r="M147" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" s="45" t="inlineStr">
+      <c r="M147" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q147" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -9653,604 +10435,659 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q148" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="10" t="inlineStr">
+      <c r="A149" s="47" t="inlineStr">
         <is>
           <t>3.15.82.025.VIE.00.000</t>
         </is>
       </c>
-      <c r="B149" s="10" t="inlineStr">
+      <c r="B149" s="47" t="inlineStr">
         <is>
           <t>SPC - Cáp đồng bọc 24KV CX(CR) 25mm2</t>
         </is>
       </c>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="C149" s="48" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="D149" s="2" t="n">
+      <c r="D149" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E149" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F149" s="4" t="n">
+      <c r="E149" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F149" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G149" s="5" t="inlineStr">
+      <c r="G149" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0032</t>
         </is>
       </c>
-      <c r="H149" s="6" t="n"/>
-      <c r="I149" s="9" t="inlineStr">
+      <c r="H149" s="48" t="n"/>
+      <c r="I149" s="47" t="inlineStr">
         <is>
           <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J149" s="43" t="n">
+      <c r="J149" s="50" t="n">
         <v>165</v>
       </c>
-      <c r="K149" s="43" t="n">
+      <c r="K149" s="50" t="n">
         <v>108950</v>
       </c>
-      <c r="L149" s="43" t="n">
+      <c r="L149" s="50" t="n">
         <v>17976750</v>
       </c>
-      <c r="M149" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N149" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P149" s="45" t="inlineStr">
+      <c r="M149" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q149" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="10" t="inlineStr">
+      <c r="A150" s="47" t="inlineStr">
         <is>
           <t>3.42.80.117.CHN.00.000</t>
         </is>
       </c>
-      <c r="B150" s="10" t="inlineStr">
+      <c r="B150" s="47" t="inlineStr">
         <is>
           <t>SPC - Chống sét van (LA) 18kv kèm phụ kiện (dòng rò &gt;= 25mm/kV)</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C150" s="48" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D150" s="2" t="n">
+      <c r="D150" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E150" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F150" s="4" t="n">
+      <c r="E150" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F150" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G150" s="5" t="inlineStr">
+      <c r="G150" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0031</t>
         </is>
       </c>
-      <c r="H150" s="6" t="n"/>
-      <c r="I150" s="9" t="inlineStr">
+      <c r="H150" s="48" t="n"/>
+      <c r="I150" s="47" t="inlineStr">
         <is>
           <t>25017 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J150" s="43" t="n">
+      <c r="J150" s="50" t="n">
         <v>12</v>
       </c>
-      <c r="K150" s="43" t="n">
+      <c r="K150" s="50" t="n">
         <v>1103000</v>
       </c>
-      <c r="L150" s="43" t="n">
+      <c r="L150" s="50" t="n">
         <v>13236000</v>
       </c>
-      <c r="M150" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N150" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P150" s="45" t="inlineStr">
+      <c r="M150" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q150" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="10" t="inlineStr">
+      <c r="A151" s="47" t="inlineStr">
         <is>
           <t>3.30.22.101.VIE.00.000</t>
         </is>
       </c>
-      <c r="B151" s="10" t="inlineStr">
+      <c r="B151" s="47" t="inlineStr">
         <is>
           <t>SPC - Cầu chì tự rơi (FCO) 15/27KV 100A Polymer</t>
         </is>
       </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="n">
+      <c r="C151" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D151" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E151" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F151" s="4" t="n">
+      <c r="E151" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F151" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G151" s="5" t="inlineStr">
+      <c r="G151" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0031</t>
         </is>
       </c>
-      <c r="H151" s="6" t="n"/>
-      <c r="I151" s="9" t="inlineStr">
+      <c r="H151" s="48" t="n"/>
+      <c r="I151" s="47" t="inlineStr">
         <is>
           <t>25017 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J151" s="43" t="n">
+      <c r="J151" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K151" s="43" t="n">
+      <c r="K151" s="50" t="n">
         <v>1553286</v>
       </c>
-      <c r="L151" s="43" t="n">
+      <c r="L151" s="50" t="n">
         <v>1553286</v>
       </c>
-      <c r="M151" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N151" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O151" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" s="45" t="inlineStr">
-        <is>
-          <t>Hạ thế</t>
+      <c r="M151" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" s="52" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q151" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="10" t="inlineStr">
+      <c r="A152" s="47" t="inlineStr">
         <is>
           <t>4.90.80.400.VIE.00.000</t>
         </is>
       </c>
-      <c r="B152" s="10" t="inlineStr">
+      <c r="B152" s="47" t="inlineStr">
         <is>
           <t>SPC - Chụp cách điện polymer cho FCO (chụp trên+ chụp dưới)</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr">
+      <c r="C152" s="48" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D152" s="2" t="n">
+      <c r="D152" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E152" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F152" s="4" t="n">
+      <c r="E152" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F152" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G152" s="5" t="inlineStr">
+      <c r="G152" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0032</t>
         </is>
       </c>
-      <c r="H152" s="6" t="n"/>
-      <c r="I152" s="9" t="inlineStr">
+      <c r="H152" s="48" t="n"/>
+      <c r="I152" s="47" t="inlineStr">
         <is>
           <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J152" s="43" t="n">
+      <c r="J152" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="K152" s="43" t="n">
+      <c r="K152" s="50" t="n">
         <v>90000</v>
       </c>
-      <c r="L152" s="43" t="n">
+      <c r="L152" s="50" t="n">
         <v>450000</v>
       </c>
-      <c r="M152" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N152" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O152" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P152" s="45" t="inlineStr">
+      <c r="M152" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q152" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="10" t="inlineStr">
+      <c r="A153" s="47" t="inlineStr">
         <is>
           <t>3.42.80.117.CHN.00.000</t>
         </is>
       </c>
-      <c r="B153" s="10" t="inlineStr">
+      <c r="B153" s="47" t="inlineStr">
         <is>
           <t>SPC - Chống sét van (LA) 18kv kèm phụ kiện (dòng rò &gt;= 25mm/kV)</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C153" s="48" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D153" s="2" t="n">
+      <c r="D153" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E153" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F153" s="4" t="n">
+      <c r="E153" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F153" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G153" s="5" t="inlineStr">
+      <c r="G153" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0036</t>
         </is>
       </c>
-      <c r="H153" s="6" t="n"/>
-      <c r="I153" s="9" t="inlineStr">
+      <c r="H153" s="48" t="n"/>
+      <c r="I153" s="47" t="inlineStr">
         <is>
           <t>25015 -SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J153" s="43" t="n">
+      <c r="J153" s="50" t="n">
         <v>12</v>
       </c>
-      <c r="K153" s="43" t="n">
+      <c r="K153" s="50" t="n">
         <v>1103000</v>
       </c>
-      <c r="L153" s="43" t="n">
+      <c r="L153" s="50" t="n">
         <v>13236000</v>
       </c>
-      <c r="M153" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N153" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O153" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P153" s="45" t="inlineStr">
+      <c r="M153" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q153" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="10" t="inlineStr">
+      <c r="A154" s="47" t="inlineStr">
         <is>
           <t>3.42.80.118.CHN.00.000</t>
         </is>
       </c>
-      <c r="B154" s="10" t="inlineStr">
+      <c r="B154" s="47" t="inlineStr">
         <is>
           <t>SPC - Chống sét van (LA) 18kV  Polymer kèm phụ kiện ( Dòng rò 31 mm/kV )</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C154" s="48" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D154" s="2" t="n">
+      <c r="D154" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E154" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F154" s="4" t="n">
+      <c r="E154" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F154" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G154" s="5" t="inlineStr">
+      <c r="G154" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0032</t>
         </is>
       </c>
-      <c r="H154" s="6" t="n"/>
-      <c r="I154" s="9" t="inlineStr">
+      <c r="H154" s="48" t="n"/>
+      <c r="I154" s="47" t="inlineStr">
         <is>
           <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J154" s="43" t="n">
+      <c r="J154" s="50" t="n">
         <v>11</v>
       </c>
-      <c r="K154" s="43" t="n">
+      <c r="K154" s="50" t="n">
         <v>1111000</v>
       </c>
-      <c r="L154" s="43" t="n">
+      <c r="L154" s="50" t="n">
         <v>12221000</v>
       </c>
-      <c r="M154" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N154" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" s="45" t="inlineStr">
-        <is>
-          <t>Hạ thế</t>
+      <c r="M154" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="52" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q154" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="10" t="inlineStr">
+      <c r="A155" s="47" t="inlineStr">
         <is>
           <t>4.90.80.400.000.00.000</t>
         </is>
       </c>
-      <c r="B155" s="10" t="inlineStr">
+      <c r="B155" s="47" t="inlineStr">
         <is>
           <t>Chụp đầu cực FCO</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="n">
+      <c r="C155" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D155" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E155" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F155" s="4" t="n">
+      <c r="E155" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F155" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G155" s="5" t="inlineStr">
+      <c r="G155" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0033</t>
         </is>
       </c>
-      <c r="H155" s="6" t="n"/>
-      <c r="I155" s="9" t="inlineStr">
+      <c r="H155" s="48" t="n"/>
+      <c r="I155" s="47" t="inlineStr">
         <is>
           <t>24025 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J155" s="43" t="n">
+      <c r="J155" s="50" t="n">
         <v>81</v>
       </c>
-      <c r="K155" s="43" t="n">
+      <c r="K155" s="50" t="n">
         <v>157500</v>
       </c>
-      <c r="L155" s="43" t="n">
+      <c r="L155" s="50" t="n">
         <v>12757500</v>
       </c>
-      <c r="M155" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N155" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O155" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P155" s="45" t="inlineStr">
+      <c r="M155" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q155" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="10" t="inlineStr">
+      <c r="A156" s="47" t="inlineStr">
         <is>
           <t>4.90.80.400.000.00.000</t>
         </is>
       </c>
-      <c r="B156" s="10" t="inlineStr">
+      <c r="B156" s="47" t="inlineStr">
         <is>
           <t>Chụp đầu cực FCO</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="n">
+      <c r="C156" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D156" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E156" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F156" s="4" t="n">
+      <c r="E156" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F156" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G156" s="5" t="inlineStr">
+      <c r="G156" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0033</t>
         </is>
       </c>
-      <c r="H156" s="6" t="n"/>
-      <c r="I156" s="9" t="inlineStr">
+      <c r="H156" s="48" t="n"/>
+      <c r="I156" s="47" t="inlineStr">
         <is>
           <t>24025 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J156" s="43" t="n">
+      <c r="J156" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K156" s="43" t="n">
+      <c r="K156" s="50" t="n">
         <v>157500</v>
       </c>
-      <c r="L156" s="43" t="n">
+      <c r="L156" s="50" t="n">
         <v>472500</v>
       </c>
-      <c r="M156" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N156" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O156" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P156" s="45" t="inlineStr">
+      <c r="M156" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q156" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="10" t="inlineStr">
+      <c r="A157" s="47" t="inlineStr">
         <is>
           <t>4.90.80.400.VIE.00.000</t>
         </is>
       </c>
-      <c r="B157" s="10" t="inlineStr">
+      <c r="B157" s="47" t="inlineStr">
         <is>
           <t>SPC - Chụp cách điện polymer cho FCO (chụp trên+ chụp dưới)</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="C157" s="48" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D157" s="2" t="n">
+      <c r="D157" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E157" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F157" s="4" t="n">
+      <c r="E157" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F157" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G157" s="5" t="inlineStr">
+      <c r="G157" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0032</t>
         </is>
       </c>
-      <c r="H157" s="6" t="n"/>
-      <c r="I157" s="9" t="inlineStr">
+      <c r="H157" s="48" t="n"/>
+      <c r="I157" s="47" t="inlineStr">
         <is>
           <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J157" s="43" t="n">
+      <c r="J157" s="50" t="n">
         <v>9</v>
       </c>
-      <c r="K157" s="43" t="n">
+      <c r="K157" s="50" t="n">
         <v>82000</v>
       </c>
-      <c r="L157" s="43" t="n">
+      <c r="L157" s="50" t="n">
         <v>738000</v>
       </c>
-      <c r="M157" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N157" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O157" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P157" s="45" t="inlineStr">
+      <c r="M157" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q157" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="10" t="inlineStr">
+      <c r="A158" s="47" t="inlineStr">
         <is>
           <t>4.90.80.400.000.00.000</t>
         </is>
       </c>
-      <c r="B158" s="10" t="inlineStr">
+      <c r="B158" s="47" t="inlineStr">
         <is>
           <t>Chụp đầu cực FCO</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="n">
+      <c r="C158" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D158" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E158" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F158" s="4" t="n">
+      <c r="E158" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F158" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G158" s="5" t="inlineStr">
+      <c r="G158" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0034</t>
         </is>
       </c>
-      <c r="H158" s="6" t="n"/>
-      <c r="I158" s="9" t="inlineStr">
+      <c r="H158" s="48" t="n"/>
+      <c r="I158" s="47" t="inlineStr">
         <is>
           <t>24026 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J158" s="43" t="n">
+      <c r="J158" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K158" s="43" t="n">
+      <c r="K158" s="50" t="n">
         <v>157500</v>
       </c>
-      <c r="L158" s="43" t="n">
+      <c r="L158" s="50" t="n">
         <v>157500</v>
       </c>
-      <c r="M158" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N158" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" s="45" t="inlineStr">
+      <c r="M158" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q158" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -10313,304 +11150,334 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q159" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="10" t="inlineStr">
+      <c r="A160" s="47" t="inlineStr">
         <is>
           <t>3.42.80.117.CHN.00.000</t>
         </is>
       </c>
-      <c r="B160" s="10" t="inlineStr">
+      <c r="B160" s="47" t="inlineStr">
         <is>
           <t>SPC - Chống sét van (LA) 18kv kèm phụ kiện (dòng rò &gt;= 25mm/kV)</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="C160" s="48" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D160" s="2" t="n">
+      <c r="D160" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E160" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F160" s="4" t="n">
+      <c r="E160" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F160" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G160" s="5" t="inlineStr">
+      <c r="G160" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0035</t>
         </is>
       </c>
-      <c r="H160" s="6" t="n"/>
-      <c r="I160" s="9" t="inlineStr">
+      <c r="H160" s="48" t="n"/>
+      <c r="I160" s="47" t="inlineStr">
         <is>
           <t>25014 -SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J160" s="43" t="n">
+      <c r="J160" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="K160" s="43" t="n">
+      <c r="K160" s="50" t="n">
         <v>1103000</v>
       </c>
-      <c r="L160" s="43" t="n">
+      <c r="L160" s="50" t="n">
         <v>19854000</v>
       </c>
-      <c r="M160" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N160" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O160" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" s="45" t="inlineStr">
+      <c r="M160" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q160" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="10" t="inlineStr">
+      <c r="A161" s="47" t="inlineStr">
         <is>
           <t>4.90.80.400.000.00.000</t>
         </is>
       </c>
-      <c r="B161" s="10" t="inlineStr">
+      <c r="B161" s="47" t="inlineStr">
         <is>
           <t>Chụp đầu cực FCO</t>
         </is>
       </c>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="n">
+      <c r="C161" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D161" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E161" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F161" s="4" t="n">
+      <c r="E161" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F161" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G161" s="5" t="inlineStr">
+      <c r="G161" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0030</t>
         </is>
       </c>
-      <c r="H161" s="6" t="n"/>
-      <c r="I161" s="9" t="inlineStr">
+      <c r="H161" s="48" t="n"/>
+      <c r="I161" s="47" t="inlineStr">
         <is>
           <t>24028 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J161" s="43" t="n">
+      <c r="J161" s="50" t="n">
         <v>222</v>
       </c>
-      <c r="K161" s="43" t="n">
+      <c r="K161" s="50" t="n">
         <v>157500</v>
       </c>
-      <c r="L161" s="43" t="n">
+      <c r="L161" s="50" t="n">
         <v>34965000</v>
       </c>
-      <c r="M161" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N161" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O161" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" s="45" t="inlineStr">
+      <c r="M161" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q161" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="10" t="inlineStr">
+      <c r="A162" s="47" t="inlineStr">
         <is>
           <t>3.15.82.025.VIE.00.000</t>
         </is>
       </c>
-      <c r="B162" s="10" t="inlineStr">
+      <c r="B162" s="47" t="inlineStr">
         <is>
           <t>SPC - Cáp đồng bọc 24KV CX(CR) 25mm2</t>
         </is>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="C162" s="48" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="D162" s="2" t="n">
+      <c r="D162" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E162" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F162" s="4" t="n">
+      <c r="E162" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F162" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G162" s="5" t="inlineStr">
+      <c r="G162" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0030</t>
         </is>
       </c>
-      <c r="H162" s="6" t="n"/>
-      <c r="I162" s="9" t="inlineStr">
+      <c r="H162" s="48" t="n"/>
+      <c r="I162" s="47" t="inlineStr">
         <is>
           <t>24028 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J162" s="43" t="n">
+      <c r="J162" s="50" t="n">
         <v>57</v>
       </c>
-      <c r="K162" s="43" t="n">
+      <c r="K162" s="50" t="n">
         <v>101800</v>
       </c>
-      <c r="L162" s="43" t="n">
+      <c r="L162" s="50" t="n">
         <v>5802600</v>
       </c>
-      <c r="M162" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N162" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O162" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P162" s="45" t="inlineStr">
+      <c r="M162" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q162" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="10" t="inlineStr">
+      <c r="A163" s="47" t="inlineStr">
         <is>
           <t>3.30.22.121.VIE.00.000</t>
         </is>
       </c>
-      <c r="B163" s="10" t="inlineStr">
+      <c r="B163" s="47" t="inlineStr">
         <is>
           <t>SPC - FCO 22kV-100A-Polyme kèm phụ kiện (dòng rò &gt;= 31mm/kV)</t>
         </is>
       </c>
-      <c r="C163" s="3" t="inlineStr">
+      <c r="C163" s="48" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D163" s="2" t="n">
+      <c r="D163" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E163" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F163" s="4" t="n">
+      <c r="E163" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F163" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G163" s="5" t="inlineStr">
+      <c r="G163" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0029</t>
         </is>
       </c>
-      <c r="H163" s="6" t="n"/>
-      <c r="I163" s="9" t="inlineStr">
+      <c r="H163" s="48" t="n"/>
+      <c r="I163" s="47" t="inlineStr">
         <is>
           <t>24017 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J163" s="43" t="n">
+      <c r="J163" s="50" t="n">
         <v>26</v>
       </c>
-      <c r="K163" s="43" t="n">
+      <c r="K163" s="50" t="n">
         <v>1338750</v>
       </c>
-      <c r="L163" s="43" t="n">
+      <c r="L163" s="50" t="n">
         <v>34807500</v>
       </c>
-      <c r="M163" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N163" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O163" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" s="45" t="inlineStr">
+      <c r="M163" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q163" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="10" t="inlineStr">
+      <c r="A164" s="47" t="inlineStr">
         <is>
           <t>3.42.80.118.CHN.00.000</t>
         </is>
       </c>
-      <c r="B164" s="10" t="inlineStr">
+      <c r="B164" s="47" t="inlineStr">
         <is>
           <t>SPC - Chống sét van (LA) 18kV  Polymer kèm phụ kiện ( Dòng rò 31 mm/kV )</t>
         </is>
       </c>
-      <c r="C164" s="3" t="inlineStr">
+      <c r="C164" s="48" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D164" s="2" t="n">
+      <c r="D164" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E164" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F164" s="4" t="n">
+      <c r="E164" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F164" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G164" s="5" t="inlineStr">
+      <c r="G164" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0029</t>
         </is>
       </c>
-      <c r="H164" s="6" t="n"/>
-      <c r="I164" s="9" t="inlineStr">
+      <c r="H164" s="48" t="n"/>
+      <c r="I164" s="47" t="inlineStr">
         <is>
           <t>24017 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J164" s="43" t="n">
+      <c r="J164" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="K164" s="43" t="n">
+      <c r="K164" s="50" t="n">
         <v>1263800</v>
       </c>
-      <c r="L164" s="43" t="n">
+      <c r="L164" s="50" t="n">
         <v>5055200</v>
       </c>
-      <c r="M164" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N164" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O164" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" s="45" t="inlineStr">
-        <is>
-          <t>Hạ thế</t>
+      <c r="M164" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" s="52" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q164" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -10673,6 +11540,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q165" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="10" t="inlineStr">
@@ -10733,124 +11605,139 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q166" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="10" t="inlineStr">
+      <c r="A167" s="47" t="inlineStr">
         <is>
           <t>4.90.80.400.000.00.000</t>
         </is>
       </c>
-      <c r="B167" s="10" t="inlineStr">
+      <c r="B167" s="47" t="inlineStr">
         <is>
           <t>Chụp đầu cực FCO</t>
         </is>
       </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="n">
+      <c r="C167" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D167" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E167" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F167" s="4" t="n">
+      <c r="E167" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F167" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G167" s="5" t="inlineStr">
+      <c r="G167" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0034</t>
         </is>
       </c>
-      <c r="H167" s="6" t="n"/>
-      <c r="I167" s="9" t="inlineStr">
+      <c r="H167" s="48" t="n"/>
+      <c r="I167" s="47" t="inlineStr">
         <is>
           <t>24026 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J167" s="43" t="n">
+      <c r="J167" s="50" t="n">
         <v>28</v>
       </c>
-      <c r="K167" s="43" t="n">
+      <c r="K167" s="50" t="n">
         <v>157500</v>
       </c>
-      <c r="L167" s="43" t="n">
+      <c r="L167" s="50" t="n">
         <v>4410000</v>
       </c>
-      <c r="M167" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N167" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O167" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" s="45" t="inlineStr">
+      <c r="M167" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q167" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="10" t="inlineStr">
+      <c r="A168" s="47" t="inlineStr">
         <is>
           <t>4.90.80.400.VIE.00.000</t>
         </is>
       </c>
-      <c r="B168" s="10" t="inlineStr">
+      <c r="B168" s="47" t="inlineStr">
         <is>
           <t>SPC - Chụp cách điện polymer cho FCO (chụp trên+ chụp dưới)</t>
         </is>
       </c>
-      <c r="C168" s="3" t="inlineStr">
+      <c r="C168" s="48" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D168" s="2" t="n">
+      <c r="D168" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E168" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F168" s="4" t="n">
+      <c r="E168" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F168" s="49" t="n">
         <v>46134</v>
       </c>
-      <c r="G168" s="5" t="inlineStr">
+      <c r="G168" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0032</t>
         </is>
       </c>
-      <c r="H168" s="6" t="n"/>
-      <c r="I168" s="9" t="inlineStr">
+      <c r="H168" s="48" t="n"/>
+      <c r="I168" s="47" t="inlineStr">
         <is>
           <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J168" s="43" t="n">
+      <c r="J168" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="K168" s="43" t="n">
+      <c r="K168" s="50" t="n">
         <v>90000</v>
       </c>
-      <c r="L168" s="43" t="n">
+      <c r="L168" s="50" t="n">
         <v>360000</v>
       </c>
-      <c r="M168" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N168" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O168" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" s="45" t="inlineStr">
+      <c r="M168" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q168" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -10913,6 +11800,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q169" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="10" t="inlineStr">
@@ -10973,6 +11865,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q170" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
@@ -11033,6 +11930,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q171" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="10" t="inlineStr">
@@ -11093,6 +11995,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q172" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
@@ -11153,6 +12060,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q173" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="10" t="inlineStr">
@@ -11213,6 +12125,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q174" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="10" t="inlineStr">
@@ -11273,6 +12190,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q175" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="10" t="inlineStr">
@@ -11333,64 +12255,74 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q176" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="10" t="inlineStr">
+      <c r="A177" s="47" t="inlineStr">
         <is>
           <t>3.56.60.121.000.00.AXX</t>
         </is>
       </c>
-      <c r="B177" s="10" t="inlineStr">
+      <c r="B177" s="47" t="inlineStr">
         <is>
           <t>Biến điện áp 22(15):V3/0,1:V3 kV - 15VA</t>
         </is>
       </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="n">
+      <c r="C177" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D177" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E177" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F177" s="4" t="n">
+      <c r="E177" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F177" s="49" t="n">
         <v>46136</v>
       </c>
-      <c r="G177" s="5" t="inlineStr">
+      <c r="G177" s="48" t="inlineStr">
         <is>
           <t>01.VH4.11.0059</t>
         </is>
       </c>
-      <c r="H177" s="6" t="n"/>
-      <c r="I177" s="9" t="inlineStr">
+      <c r="H177" s="48" t="n"/>
+      <c r="I177" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập lại  TU, TI SCL T4-2026 03.VH4.41.0026</t>
         </is>
       </c>
-      <c r="J177" s="43" t="n">
+      <c r="J177" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K177" s="43" t="n">
+      <c r="K177" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L177" s="43" t="n">
+      <c r="L177" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M177" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N177" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O177" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P177" s="45" t="inlineStr">
+      <c r="M177" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q177" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -11453,6 +12385,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q178" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="10" t="inlineStr">
@@ -11513,184 +12450,204 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q179" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="10" t="inlineStr">
+      <c r="A180" s="47" t="inlineStr">
         <is>
           <t>3.53.65.148.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B180" s="10" t="inlineStr">
+      <c r="B180" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 50-100/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="n">
+      <c r="C180" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D180" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E180" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F180" s="4" t="n">
+      <c r="E180" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F180" s="49" t="n">
         <v>46140</v>
       </c>
-      <c r="G180" s="5" t="inlineStr">
+      <c r="G180" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H180" s="6" t="n"/>
-      <c r="I180" s="9" t="inlineStr">
+      <c r="H180" s="48" t="n"/>
+      <c r="I180" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J180" s="43" t="n">
+      <c r="J180" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K180" s="43" t="n">
+      <c r="K180" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L180" s="43" t="n">
+      <c r="L180" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="M180" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O180" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" s="45" t="inlineStr">
+      <c r="M180" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q180" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="10" t="inlineStr">
+      <c r="A181" s="47" t="inlineStr">
         <is>
           <t>3.56.60.032.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B181" s="10" t="inlineStr">
+      <c r="B181" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp (TU 1P 12000/120V-15VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="n">
+      <c r="C181" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D181" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E181" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F181" s="4" t="n">
+      <c r="E181" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F181" s="49" t="n">
         <v>46140</v>
       </c>
-      <c r="G181" s="5" t="inlineStr">
+      <c r="G181" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H181" s="6" t="n"/>
-      <c r="I181" s="9" t="inlineStr">
+      <c r="H181" s="48" t="n"/>
+      <c r="I181" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J181" s="43" t="n">
+      <c r="J181" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="K181" s="43" t="n">
+      <c r="K181" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L181" s="43" t="n">
+      <c r="L181" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="M181" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O181" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P181" s="45" t="inlineStr">
+      <c r="M181" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q181" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="10" t="inlineStr">
+      <c r="A182" s="47" t="inlineStr">
         <is>
           <t>3.53.65.015.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B182" s="10" t="inlineStr">
+      <c r="B182" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 15-30/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C182" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="n">
+      <c r="C182" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D182" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E182" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F182" s="4" t="n">
+      <c r="E182" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F182" s="49" t="n">
         <v>46140</v>
       </c>
-      <c r="G182" s="5" t="inlineStr">
+      <c r="G182" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H182" s="6" t="n"/>
-      <c r="I182" s="9" t="inlineStr">
+      <c r="H182" s="48" t="n"/>
+      <c r="I182" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J182" s="43" t="n">
+      <c r="J182" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K182" s="43" t="n">
+      <c r="K182" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L182" s="43" t="n">
+      <c r="L182" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M182" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O182" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" s="45" t="inlineStr">
+      <c r="M182" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q182" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -11753,6 +12710,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q183" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="10" t="inlineStr">
@@ -11813,6 +12775,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q184" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="10" t="inlineStr">
@@ -11873,6 +12840,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q185" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="10" t="inlineStr">
@@ -11933,6 +12905,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q186" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="10" t="inlineStr">
@@ -11993,64 +12970,74 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q187" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="188">
-      <c r="A188" s="10" t="inlineStr">
+      <c r="A188" s="47" t="inlineStr">
         <is>
           <t>3.53.65.152.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B188" s="10" t="inlineStr">
+      <c r="B188" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 150-300/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C188" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="n">
+      <c r="C188" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D188" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E188" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F188" s="4" t="n">
+      <c r="E188" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F188" s="49" t="n">
         <v>46140</v>
       </c>
-      <c r="G188" s="5" t="inlineStr">
+      <c r="G188" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H188" s="6" t="n"/>
-      <c r="I188" s="9" t="inlineStr">
+      <c r="H188" s="48" t="n"/>
+      <c r="I188" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J188" s="43" t="n">
+      <c r="J188" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K188" s="43" t="n">
+      <c r="K188" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L188" s="43" t="n">
+      <c r="L188" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M188" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N188" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O188" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P188" s="45" t="inlineStr">
+      <c r="M188" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q188" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -12113,6 +13100,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q189" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
@@ -12173,6 +13165,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q190" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="10" t="inlineStr">
@@ -12233,6 +13230,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q191" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="10" t="inlineStr">
@@ -12293,6 +13295,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q192" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="10" t="inlineStr">
@@ -12353,6 +13360,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q193" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="10" t="inlineStr">
@@ -12413,6 +13425,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q194" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="10" t="inlineStr">
@@ -12473,6 +13490,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q195" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="10" t="inlineStr">
@@ -12533,6 +13555,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q196" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="10" t="inlineStr">
@@ -12593,6 +13620,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q197" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="10" t="inlineStr">
@@ -12653,6 +13685,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q198" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="10" t="inlineStr">
@@ -12713,6 +13750,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q199" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="10" t="inlineStr">
@@ -12773,64 +13815,74 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q200" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="10" t="inlineStr">
+      <c r="A201" s="47" t="inlineStr">
         <is>
           <t>3.56.60.032.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B201" s="10" t="inlineStr">
+      <c r="B201" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp (TU 1P 12000/120V-15VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C201" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="n">
+      <c r="C201" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D201" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E201" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F201" s="4" t="n">
+      <c r="E201" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F201" s="49" t="n">
         <v>46140</v>
       </c>
-      <c r="G201" s="5" t="inlineStr">
+      <c r="G201" s="48" t="inlineStr">
         <is>
           <t>01.VH8.12.0037</t>
         </is>
       </c>
-      <c r="H201" s="6" t="n"/>
-      <c r="I201" s="9" t="inlineStr">
+      <c r="H201" s="48" t="n"/>
+      <c r="I201" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J201" s="43" t="n">
+      <c r="J201" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K201" s="43" t="n">
+      <c r="K201" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L201" s="43" t="n">
+      <c r="L201" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M201" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N201" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O201" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P201" s="45" t="inlineStr">
+      <c r="M201" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q201" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -12893,6 +13945,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q202" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="10" t="inlineStr">
@@ -12953,6 +14010,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q203" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="10" t="inlineStr">
@@ -13013,6 +14075,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q204" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="10" t="inlineStr">
@@ -13073,64 +14140,74 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q205" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="206">
-      <c r="A206" s="10" t="inlineStr">
+      <c r="A206" s="47" t="inlineStr">
         <is>
           <t>3.53.65.015.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B206" s="10" t="inlineStr">
+      <c r="B206" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 15-30/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C206" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="n">
+      <c r="C206" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D206" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E206" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F206" s="4" t="n">
+      <c r="E206" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F206" s="49" t="n">
         <v>46140</v>
       </c>
-      <c r="G206" s="5" t="inlineStr">
+      <c r="G206" s="48" t="inlineStr">
         <is>
           <t>01.VH8.12.0037</t>
         </is>
       </c>
-      <c r="H206" s="6" t="n"/>
-      <c r="I206" s="9" t="inlineStr">
+      <c r="H206" s="48" t="n"/>
+      <c r="I206" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J206" s="43" t="n">
+      <c r="J206" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K206" s="43" t="n">
+      <c r="K206" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L206" s="43" t="n">
+      <c r="L206" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M206" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N206" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O206" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P206" s="45" t="inlineStr">
+      <c r="M206" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q206" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -13193,6 +14270,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q207" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="10" t="inlineStr">
@@ -13253,6 +14335,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q208" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="10" t="inlineStr">
@@ -13313,6 +14400,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q209" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="10" t="inlineStr">
@@ -13373,6 +14465,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q210" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="10" t="inlineStr">
@@ -13433,6 +14530,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q211" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="10" t="inlineStr">
@@ -13493,6 +14595,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q212" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="10" t="inlineStr">
@@ -13553,6 +14660,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q213" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="10" t="inlineStr">
@@ -13613,6 +14725,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q214" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="10" t="inlineStr">
@@ -13673,6 +14790,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q215" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="10" t="inlineStr">
@@ -13733,6 +14855,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q216" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="10" t="inlineStr">
@@ -13793,6 +14920,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q217" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="10" t="inlineStr">
@@ -13853,6 +14985,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q218" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="10" t="inlineStr">
@@ -13913,6 +15050,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q219" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="10" t="inlineStr">
@@ -13973,6 +15115,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q220" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="10" t="inlineStr">
@@ -14033,6 +15180,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q221" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="10" t="inlineStr">
@@ -14093,6 +15245,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q222" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="10" t="inlineStr">
@@ -14153,6 +15310,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q223" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="10" t="inlineStr">
@@ -14213,6 +15375,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q224" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="10" t="inlineStr">
@@ -14273,6 +15440,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q225" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="10" t="inlineStr">
@@ -14333,6 +15505,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q226" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="10" t="inlineStr">
@@ -14393,6 +15570,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q227" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="10" t="inlineStr">
@@ -14453,6 +15635,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q228" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
@@ -14513,6 +15700,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q229" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
@@ -14573,6 +15765,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q230" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
@@ -14633,6 +15830,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q231" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="10" t="inlineStr">
@@ -14693,6 +15895,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q232" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="10" t="inlineStr">
@@ -14753,6 +15960,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q233" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="10" t="inlineStr">
@@ -14813,6 +16025,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q234" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="10" t="inlineStr">
@@ -14873,6 +16090,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q235" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="10" t="inlineStr">
@@ -14933,6 +16155,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q236" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="10" t="inlineStr">
@@ -14993,6 +16220,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q237" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="10" t="inlineStr">
@@ -15053,6 +16285,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q238" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="10" t="inlineStr">
@@ -15113,6 +16350,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q239" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="10" t="inlineStr">
@@ -15173,6 +16415,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q240" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="10" t="inlineStr">
@@ -15233,6 +16480,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q241" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="10" t="inlineStr">
@@ -15293,6 +16545,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q242" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="10" t="inlineStr">
@@ -15353,64 +16610,74 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q243" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="244">
-      <c r="A244" s="10" t="inlineStr">
+      <c r="A244" s="47" t="inlineStr">
         <is>
           <t>3.53.05.203.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B244" s="10" t="inlineStr">
+      <c r="B244" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 200/5A</t>
         </is>
       </c>
-      <c r="C244" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="n">
+      <c r="C244" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D244" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E244" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F244" s="4" t="n">
+      <c r="E244" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F244" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G244" s="5" t="inlineStr">
+      <c r="G244" s="48" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H244" s="6" t="n"/>
-      <c r="I244" s="9" t="inlineStr">
+      <c r="H244" s="48" t="n"/>
+      <c r="I244" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J244" s="43" t="n">
+      <c r="J244" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="K244" s="43" t="n">
+      <c r="K244" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L244" s="43" t="n">
+      <c r="L244" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="M244" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N244" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O244" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P244" s="45" t="inlineStr">
+      <c r="M244" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="Q244" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -15473,6 +16740,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q245" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="10" t="inlineStr">
@@ -15533,6 +16805,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q246" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="10" t="inlineStr">
@@ -15593,6 +16870,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q247" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="10" t="inlineStr">
@@ -15653,6 +16935,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q248" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="10" t="inlineStr">
@@ -15713,6 +17000,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q249" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="10" t="inlineStr">
@@ -15773,6 +17065,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q250" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="10" t="inlineStr">
@@ -15833,6 +17130,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q251" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="10" t="inlineStr">
@@ -15893,6 +17195,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q252" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="10" t="inlineStr">
@@ -15953,6 +17260,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q253" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="10" t="inlineStr">
@@ -16013,6 +17325,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q254" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="10" t="inlineStr">
@@ -16073,6 +17390,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q255" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="10" t="inlineStr">
@@ -16133,6 +17455,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q256" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="10" t="inlineStr">
@@ -16193,6 +17520,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q257" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="10" t="inlineStr">
@@ -16253,6 +17585,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q258" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="10" t="inlineStr">
@@ -16313,6 +17650,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q259" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="10" t="inlineStr">
@@ -16373,6 +17715,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q260" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="10" t="inlineStr">
@@ -16430,7 +17777,12 @@
       </c>
       <c r="P261" s="45" t="inlineStr">
         <is>
-          <t>Hạ thế</t>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q261" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
         </is>
       </c>
     </row>
@@ -16493,124 +17845,139 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q262" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="263">
-      <c r="A263" s="10" t="inlineStr">
+      <c r="A263" s="47" t="inlineStr">
         <is>
           <t>3.53.05.150.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B263" s="10" t="inlineStr">
+      <c r="B263" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 150/5A 5VA CCX 0,5</t>
         </is>
       </c>
-      <c r="C263" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="n">
+      <c r="C263" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D263" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E263" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F263" s="4" t="n">
+      <c r="E263" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F263" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G263" s="5" t="inlineStr">
+      <c r="G263" s="48" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H263" s="6" t="n"/>
-      <c r="I263" s="9" t="inlineStr">
+      <c r="H263" s="48" t="n"/>
+      <c r="I263" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J263" s="43" t="n">
+      <c r="J263" s="50" t="n">
         <v>25</v>
       </c>
-      <c r="K263" s="43" t="n">
+      <c r="K263" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L263" s="43" t="n">
+      <c r="L263" s="50" t="n">
         <v>25</v>
       </c>
-      <c r="M263" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N263" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O263" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P263" s="45" t="inlineStr">
+      <c r="M263" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N263" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q263" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="264">
-      <c r="A264" s="10" t="inlineStr">
+      <c r="A264" s="47" t="inlineStr">
         <is>
           <t>3.53.05.314.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B264" s="10" t="inlineStr">
+      <c r="B264" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 300/5A</t>
         </is>
       </c>
-      <c r="C264" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="n">
+      <c r="C264" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D264" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E264" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F264" s="4" t="n">
+      <c r="E264" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F264" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G264" s="5" t="inlineStr">
+      <c r="G264" s="48" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H264" s="6" t="n"/>
-      <c r="I264" s="9" t="inlineStr">
+      <c r="H264" s="48" t="n"/>
+      <c r="I264" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J264" s="43" t="n">
+      <c r="J264" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="K264" s="43" t="n">
+      <c r="K264" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L264" s="43" t="n">
+      <c r="L264" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="M264" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N264" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O264" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P264" s="45" t="inlineStr">
+      <c r="M264" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="Q264" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -16673,6 +18040,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q265" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="10" t="inlineStr">
@@ -16733,6 +18105,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q266" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="10" t="inlineStr">
@@ -16790,7 +18167,12 @@
       </c>
       <c r="P267" s="45" t="inlineStr">
         <is>
-          <t>Hạ thế</t>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q267" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
         </is>
       </c>
     </row>
@@ -16853,6 +18235,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q268" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="10" t="inlineStr">
@@ -16913,6 +18300,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q269" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="10" t="inlineStr">
@@ -16973,6 +18365,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q270" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="10" t="inlineStr">
@@ -17033,544 +18430,594 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q271" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="272">
-      <c r="A272" s="10" t="inlineStr">
+      <c r="A272" s="47" t="inlineStr">
         <is>
           <t>3.53.05.105.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B272" s="10" t="inlineStr">
+      <c r="B272" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 100/5A</t>
         </is>
       </c>
-      <c r="C272" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="n">
+      <c r="C272" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D272" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E272" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F272" s="4" t="n">
+      <c r="E272" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F272" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G272" s="5" t="inlineStr">
+      <c r="G272" s="48" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H272" s="6" t="n"/>
-      <c r="I272" s="9" t="inlineStr">
+      <c r="H272" s="48" t="n"/>
+      <c r="I272" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J272" s="43" t="n">
+      <c r="J272" s="50" t="n">
         <v>11</v>
       </c>
-      <c r="K272" s="43" t="n">
+      <c r="K272" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L272" s="43" t="n">
+      <c r="L272" s="50" t="n">
         <v>11</v>
       </c>
-      <c r="M272" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N272" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O272" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P272" s="45" t="inlineStr">
+      <c r="M272" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N272" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P272" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q272" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="273">
-      <c r="A273" s="10" t="inlineStr">
+      <c r="A273" s="47" t="inlineStr">
         <is>
           <t>3.53.05.150.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B273" s="10" t="inlineStr">
+      <c r="B273" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 150/5A 5VA CCX 0,5</t>
         </is>
       </c>
-      <c r="C273" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="n">
+      <c r="C273" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D273" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E273" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F273" s="4" t="n">
+      <c r="E273" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F273" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G273" s="5" t="inlineStr">
+      <c r="G273" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H273" s="6" t="n"/>
-      <c r="I273" s="9" t="inlineStr">
+      <c r="H273" s="48" t="n"/>
+      <c r="I273" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J273" s="43" t="n">
+      <c r="J273" s="50" t="n">
         <v>15</v>
       </c>
-      <c r="K273" s="43" t="n">
+      <c r="K273" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L273" s="43" t="n">
+      <c r="L273" s="50" t="n">
         <v>15</v>
       </c>
-      <c r="M273" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N273" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O273" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P273" s="45" t="inlineStr">
+      <c r="M273" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N273" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q273" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="274">
-      <c r="A274" s="10" t="inlineStr">
+      <c r="A274" s="47" t="inlineStr">
         <is>
           <t>3.53.05.320.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B274" s="10" t="inlineStr">
+      <c r="B274" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 800/5A</t>
         </is>
       </c>
-      <c r="C274" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="n">
+      <c r="C274" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D274" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E274" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F274" s="4" t="n">
+      <c r="E274" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F274" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G274" s="5" t="inlineStr">
+      <c r="G274" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H274" s="6" t="n"/>
-      <c r="I274" s="9" t="inlineStr">
+      <c r="H274" s="48" t="n"/>
+      <c r="I274" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J274" s="43" t="n">
+      <c r="J274" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K274" s="43" t="n">
+      <c r="K274" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L274" s="43" t="n">
+      <c r="L274" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="M274" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N274" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O274" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P274" s="45" t="inlineStr">
+      <c r="M274" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N274" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q274" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="275">
-      <c r="A275" s="10" t="inlineStr">
+      <c r="A275" s="47" t="inlineStr">
         <is>
           <t>3.53.05.334.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B275" s="10" t="inlineStr">
+      <c r="B275" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 1000/5A-5VA-CCX 0,5</t>
         </is>
       </c>
-      <c r="C275" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="n">
+      <c r="C275" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D275" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E275" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F275" s="4" t="n">
+      <c r="E275" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F275" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G275" s="5" t="inlineStr">
+      <c r="G275" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H275" s="6" t="n"/>
-      <c r="I275" s="9" t="inlineStr">
+      <c r="H275" s="48" t="n"/>
+      <c r="I275" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J275" s="43" t="n">
+      <c r="J275" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="K275" s="43" t="n">
+      <c r="K275" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L275" s="43" t="n">
+      <c r="L275" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="M275" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N275" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O275" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P275" s="45" t="inlineStr">
+      <c r="M275" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N275" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P275" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q275" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="276">
-      <c r="A276" s="10" t="inlineStr">
+      <c r="A276" s="47" t="inlineStr">
         <is>
           <t>3.56.60.224.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B276" s="10" t="inlineStr">
+      <c r="B276" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp (TU) 24KV 22000/√3/100/√3V 15VA CCX0,5</t>
         </is>
       </c>
-      <c r="C276" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="n">
+      <c r="C276" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D276" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E276" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F276" s="4" t="n">
+      <c r="E276" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F276" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G276" s="5" t="inlineStr">
+      <c r="G276" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H276" s="6" t="n"/>
-      <c r="I276" s="9" t="inlineStr">
+      <c r="H276" s="48" t="n"/>
+      <c r="I276" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J276" s="43" t="n">
+      <c r="J276" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="K276" s="43" t="n">
+      <c r="K276" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L276" s="43" t="n">
+      <c r="L276" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="M276" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N276" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O276" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P276" s="45" t="inlineStr">
+      <c r="M276" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N276" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q276" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="277">
-      <c r="A277" s="10" t="inlineStr">
+      <c r="A277" s="47" t="inlineStr">
         <is>
           <t>3.53.05.264.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B277" s="10" t="inlineStr">
+      <c r="B277" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 250/5A</t>
         </is>
       </c>
-      <c r="C277" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D277" s="2" t="n">
+      <c r="C277" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D277" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E277" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F277" s="4" t="n">
+      <c r="E277" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F277" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G277" s="5" t="inlineStr">
+      <c r="G277" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H277" s="6" t="n"/>
-      <c r="I277" s="9" t="inlineStr">
+      <c r="H277" s="48" t="n"/>
+      <c r="I277" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J277" s="43" t="n">
+      <c r="J277" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="K277" s="43" t="n">
+      <c r="K277" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L277" s="43" t="n">
+      <c r="L277" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="M277" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N277" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O277" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P277" s="45" t="inlineStr">
+      <c r="M277" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q277" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="278">
-      <c r="A278" s="10" t="inlineStr">
+      <c r="A278" s="47" t="inlineStr">
         <is>
           <t>3.53.05.319.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B278" s="10" t="inlineStr">
+      <c r="B278" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 600/5A</t>
         </is>
       </c>
-      <c r="C278" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D278" s="2" t="n">
+      <c r="C278" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D278" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E278" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F278" s="4" t="n">
+      <c r="E278" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F278" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G278" s="5" t="inlineStr">
+      <c r="G278" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H278" s="6" t="n"/>
-      <c r="I278" s="9" t="inlineStr">
+      <c r="H278" s="48" t="n"/>
+      <c r="I278" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J278" s="43" t="n">
+      <c r="J278" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K278" s="43" t="n">
+      <c r="K278" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L278" s="43" t="n">
+      <c r="L278" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="M278" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N278" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O278" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P278" s="45" t="inlineStr">
+      <c r="M278" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q278" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="279">
-      <c r="A279" s="10" t="inlineStr">
+      <c r="A279" s="47" t="inlineStr">
         <is>
           <t>3.53.05.330.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B279" s="10" t="inlineStr">
+      <c r="B279" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 400/5A-5VA-CCX 0,5</t>
         </is>
       </c>
-      <c r="C279" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D279" s="2" t="n">
+      <c r="C279" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D279" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E279" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F279" s="4" t="n">
+      <c r="E279" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F279" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G279" s="5" t="inlineStr">
+      <c r="G279" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H279" s="6" t="n"/>
-      <c r="I279" s="9" t="inlineStr">
+      <c r="H279" s="48" t="n"/>
+      <c r="I279" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J279" s="43" t="n">
+      <c r="J279" s="50" t="n">
         <v>17</v>
       </c>
-      <c r="K279" s="43" t="n">
+      <c r="K279" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L279" s="43" t="n">
+      <c r="L279" s="50" t="n">
         <v>17</v>
       </c>
-      <c r="M279" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N279" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P279" s="45" t="inlineStr">
+      <c r="M279" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q279" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="280">
-      <c r="A280" s="10" t="inlineStr">
+      <c r="A280" s="47" t="inlineStr">
         <is>
           <t>3.53.05.203.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B280" s="10" t="inlineStr">
+      <c r="B280" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 200/5A</t>
         </is>
       </c>
-      <c r="C280" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D280" s="2" t="n">
+      <c r="C280" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D280" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E280" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F280" s="4" t="n">
+      <c r="E280" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F280" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G280" s="5" t="inlineStr">
+      <c r="G280" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H280" s="6" t="n"/>
-      <c r="I280" s="9" t="inlineStr">
+      <c r="H280" s="48" t="n"/>
+      <c r="I280" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J280" s="43" t="n">
+      <c r="J280" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K280" s="43" t="n">
+      <c r="K280" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L280" s="43" t="n">
+      <c r="L280" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="M280" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N280" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O280" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P280" s="45" t="inlineStr">
+      <c r="M280" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="Q280" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -17633,124 +19080,139 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q281" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="282">
-      <c r="A282" s="10" t="inlineStr">
+      <c r="A282" s="47" t="inlineStr">
         <is>
           <t>3.53.05.318.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B282" s="10" t="inlineStr">
+      <c r="B282" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 500/5A</t>
         </is>
       </c>
-      <c r="C282" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="n">
+      <c r="C282" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D282" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E282" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F282" s="4" t="n">
+      <c r="E282" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F282" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G282" s="5" t="inlineStr">
+      <c r="G282" s="48" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H282" s="6" t="n"/>
-      <c r="I282" s="9" t="inlineStr">
+      <c r="H282" s="48" t="n"/>
+      <c r="I282" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J282" s="43" t="n">
+      <c r="J282" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="K282" s="43" t="n">
+      <c r="K282" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L282" s="43" t="n">
+      <c r="L282" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="M282" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N282" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O282" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P282" s="45" t="inlineStr">
+      <c r="M282" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q282" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
+        </is>
+      </c>
     </row>
     <row r="283">
-      <c r="A283" s="10" t="inlineStr">
+      <c r="A283" s="47" t="inlineStr">
         <is>
           <t>3.53.05.318.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B283" s="10" t="inlineStr">
+      <c r="B283" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 500/5A</t>
         </is>
       </c>
-      <c r="C283" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D283" s="2" t="n">
+      <c r="C283" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D283" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E283" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F283" s="4" t="n">
+      <c r="E283" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F283" s="49" t="n">
         <v>46155</v>
       </c>
-      <c r="G283" s="5" t="inlineStr">
+      <c r="G283" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H283" s="6" t="n"/>
-      <c r="I283" s="9" t="inlineStr">
+      <c r="H283" s="48" t="n"/>
+      <c r="I283" s="47" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J283" s="43" t="n">
+      <c r="J283" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K283" s="43" t="n">
+      <c r="K283" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L283" s="43" t="n">
+      <c r="L283" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="M283" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N283" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O283" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P283" s="45" t="inlineStr">
+      <c r="M283" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N283" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="Q283" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -17813,64 +19275,74 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q284" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="285">
-      <c r="A285" s="10" t="inlineStr">
+      <c r="A285" s="47" t="inlineStr">
         <is>
           <t>3.56.60.016.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B285" s="10" t="inlineStr">
+      <c r="B285" s="47" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp TU 12000/120V</t>
         </is>
       </c>
-      <c r="C285" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D285" s="2" t="n">
+      <c r="C285" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D285" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E285" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F285" s="4" t="n">
+      <c r="E285" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F285" s="49" t="n">
         <v>46157</v>
       </c>
-      <c r="G285" s="5" t="inlineStr">
+      <c r="G285" s="48" t="inlineStr">
         <is>
           <t>01.VH4.12.0045</t>
         </is>
       </c>
-      <c r="H285" s="6" t="n"/>
-      <c r="I285" s="9" t="inlineStr">
+      <c r="H285" s="48" t="n"/>
+      <c r="I285" s="47" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TU SCL T5-2026</t>
         </is>
       </c>
-      <c r="J285" s="43" t="n">
+      <c r="J285" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="K285" s="43" t="n">
+      <c r="K285" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L285" s="43" t="n">
+      <c r="L285" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="M285" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N285" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O285" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P285" s="45" t="inlineStr">
+      <c r="M285" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N285" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q285" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -17933,6 +19405,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q286" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="10" t="inlineStr">
@@ -17993,6 +19470,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q287" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="10" t="inlineStr">
@@ -18050,7 +19532,12 @@
       </c>
       <c r="P288" s="45" t="inlineStr">
         <is>
-          <t>Hạ thế</t>
+          <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q288" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
         </is>
       </c>
     </row>
@@ -18113,6 +19600,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q289" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="10" t="inlineStr">
@@ -18173,6 +19665,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q290" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="10" t="inlineStr">
@@ -18233,6 +19730,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q291" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="10" t="inlineStr">
@@ -18293,6 +19795,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q292" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="10" t="inlineStr">
@@ -18353,64 +19860,74 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q293" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="294">
-      <c r="A294" s="10" t="inlineStr">
+      <c r="A294" s="47" t="inlineStr">
         <is>
           <t>3.15.42.120.VIE.00.000</t>
         </is>
       </c>
-      <c r="B294" s="10" t="inlineStr">
+      <c r="B294" s="47" t="inlineStr">
         <is>
           <t>SPC - Cáp đồng bọc hạ thế CV 120mm2</t>
         </is>
       </c>
-      <c r="C294" s="3" t="inlineStr">
+      <c r="C294" s="48" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="D294" s="2" t="n">
+      <c r="D294" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E294" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F294" s="4" t="n">
+      <c r="E294" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F294" s="49" t="n">
         <v>46162</v>
       </c>
-      <c r="G294" s="5" t="inlineStr">
+      <c r="G294" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0050</t>
         </is>
       </c>
-      <c r="H294" s="6" t="n"/>
-      <c r="I294" s="9" t="inlineStr">
+      <c r="H294" s="48" t="n"/>
+      <c r="I294" s="47" t="inlineStr">
         <is>
           <t>24025-SX:Nhập Vtư từ Ctr 24025 đ/c SXKD cấp cho Ctr SCL TBA 2026-Cty Quang Vũ Thi công</t>
         </is>
       </c>
-      <c r="J294" s="43" t="n">
+      <c r="J294" s="50" t="n">
         <v>15.5</v>
       </c>
-      <c r="K294" s="43" t="n">
+      <c r="K294" s="50" t="n">
         <v>355200</v>
       </c>
-      <c r="L294" s="43" t="n">
+      <c r="L294" s="50" t="n">
         <v>5505600</v>
       </c>
-      <c r="M294" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N294" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O294" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P294" s="45" t="inlineStr">
+      <c r="M294" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N294" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="Q294" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -18473,6 +19990,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q295" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="10" t="inlineStr">
@@ -18533,64 +20055,74 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q296" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="297">
-      <c r="A297" s="10" t="inlineStr">
+      <c r="A297" s="47" t="inlineStr">
         <is>
           <t>3.30.92.025.VIE.00.000</t>
         </is>
       </c>
-      <c r="B297" s="10" t="inlineStr">
+      <c r="B297" s="47" t="inlineStr">
         <is>
           <t>SPC - Dây chì (FUSE LINK) 25A</t>
         </is>
       </c>
-      <c r="C297" s="3" t="inlineStr">
+      <c r="C297" s="48" t="inlineStr">
         <is>
           <t>Sợi</t>
         </is>
       </c>
-      <c r="D297" s="2" t="n">
+      <c r="D297" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E297" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F297" s="4" t="n">
+      <c r="E297" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F297" s="49" t="n">
         <v>46167</v>
       </c>
-      <c r="G297" s="5" t="inlineStr">
+      <c r="G297" s="48" t="inlineStr">
         <is>
           <t>01.VH6.11.0002</t>
         </is>
       </c>
-      <c r="H297" s="6" t="n"/>
-      <c r="I297" s="9" t="inlineStr">
+      <c r="H297" s="48" t="n"/>
+      <c r="I297" s="47" t="inlineStr">
         <is>
           <t>VTAD2606002-Nhập Vtư trả lại kho VHJ (PX 02.VH6.41.0006/24.04.26; 07.VHJ.56.0001/24.04.26)</t>
         </is>
       </c>
-      <c r="J297" s="43" t="n">
+      <c r="J297" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="K297" s="43" t="n">
+      <c r="K297" s="50" t="n">
         <v>46000</v>
       </c>
-      <c r="L297" s="43" t="n">
+      <c r="L297" s="50" t="n">
         <v>138000</v>
       </c>
-      <c r="M297" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N297" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O297" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P297" s="45" t="inlineStr">
+      <c r="M297" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N297" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P297" s="52" t="inlineStr">
         <is>
           <t>Trung thế</t>
+        </is>
+      </c>
+      <c r="Q297" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -18653,6 +20185,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q298" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="10" t="inlineStr">
@@ -18713,6 +20250,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q299" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="10" t="inlineStr">
@@ -18773,6 +20315,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q300" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="10" t="inlineStr">
@@ -18833,6 +20380,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q301" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="10" t="inlineStr">
@@ -18893,6 +20445,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q302" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="10" t="inlineStr">
@@ -18953,6 +20510,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q303" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="10" t="inlineStr">
@@ -19013,6 +20575,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q304" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="10" t="inlineStr">
@@ -19073,6 +20640,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q305" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="10" t="inlineStr">
@@ -19133,6 +20705,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q306" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="10" t="inlineStr">
@@ -19193,64 +20770,74 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q307" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="308">
-      <c r="A308" s="10" t="inlineStr">
+      <c r="A308" s="47" t="inlineStr">
         <is>
           <t>3.20.84.240.VIE.00.000</t>
         </is>
       </c>
-      <c r="B308" s="10" t="inlineStr">
+      <c r="B308" s="47" t="inlineStr">
         <is>
           <t>SPC - Đầu cosse ép đồng 240mm2</t>
         </is>
       </c>
-      <c r="C308" s="3" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D308" s="2" t="n">
+      <c r="C308" s="48" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D308" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E308" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F308" s="4" t="n">
+      <c r="E308" s="48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F308" s="49" t="n">
         <v>46170</v>
       </c>
-      <c r="G308" s="5" t="inlineStr">
+      <c r="G308" s="48" t="inlineStr">
         <is>
           <t>01.VH1.16.0052</t>
         </is>
       </c>
-      <c r="H308" s="6" t="n"/>
-      <c r="I308" s="9" t="inlineStr">
+      <c r="H308" s="48" t="n"/>
+      <c r="I308" s="47" t="inlineStr">
         <is>
           <t>24027-SX:Nhập Vtư từ Ctr 24027 đ/c SXKD cấp cho Ctr SCL TBA 2026-Cty Quang Vũ Thi công</t>
         </is>
       </c>
-      <c r="J308" s="43" t="n">
+      <c r="J308" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="K308" s="43" t="n">
+      <c r="K308" s="50" t="n">
         <v>131100</v>
       </c>
-      <c r="L308" s="43" t="n">
+      <c r="L308" s="50" t="n">
         <v>655500</v>
       </c>
-      <c r="M308" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N308" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O308" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P308" s="45" t="inlineStr">
+      <c r="M308" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N308" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P308" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="Q308" s="53" t="inlineStr">
+        <is>
+          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -19313,6 +20900,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q309" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="10" t="inlineStr">
@@ -19373,6 +20965,11 @@
           <t>Trung thế</t>
         </is>
       </c>
+      <c r="Q310" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="10" t="inlineStr">
@@ -19433,6 +21030,11 @@
           <t>Hạ thế</t>
         </is>
       </c>
+      <c r="Q311" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="10" t="inlineStr">
@@ -19491,6 +21093,11 @@
       <c r="P312" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
+        </is>
+      </c>
+      <c r="Q312" s="46" t="inlineStr">
+        <is>
+          <t>Xuất công trình</t>
         </is>
       </c>
     </row>

--- a/TachPP_BL_ChiTiet.xlsx
+++ b/TachPP_BL_ChiTiet.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="5">
     <font>
       <name val="Times New Roman"/>
       <family val="2"/>
@@ -53,26 +53,8 @@
       <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Times New Roman"/>
-      <color rgb="001A5276"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <i val="1"/>
-      <color rgb="007B3F00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="00C0392B"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -89,11 +71,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD580"/>
       </patternFill>
     </fill>
   </fills>
@@ -263,7 +240,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -386,30 +363,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -810,7 +763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q312"/>
+  <dimension ref="A1:P312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.6"/>
   <cols>
     <col width="15.796875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -886,11 +839,6 @@
           <t>Trung/Hạ thế</t>
         </is>
       </c>
-      <c r="Q1" s="37" t="inlineStr">
-        <is>
-          <t>Loại giao dịch</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="14.4" customFormat="1" customHeight="1" s="20">
       <c r="A2" s="38" t="n"/>
@@ -945,11 +893,6 @@
           <t>PHÂN LOẠI</t>
         </is>
       </c>
-      <c r="Q2" s="25" t="inlineStr">
-        <is>
-          <t>XUẤT / THU HỒI</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -1010,11 +953,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q3" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -1075,11 +1013,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q4" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -1140,11 +1073,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q5" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -1205,11 +1133,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q6" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -1270,11 +1193,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q7" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -1335,11 +1253,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q8" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -1400,11 +1313,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q9" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1465,11 +1373,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q10" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1530,11 +1433,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q11" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -1595,11 +1493,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q12" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1660,11 +1553,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q13" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -1725,11 +1613,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q14" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -1790,11 +1673,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q15" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -1855,11 +1733,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q16" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -1920,11 +1793,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q17" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -1985,11 +1853,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q18" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -2050,11 +1913,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q19" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -2115,11 +1973,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q20" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2180,11 +2033,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q21" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2245,11 +2093,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q22" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2310,11 +2153,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q23" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2375,11 +2213,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q24" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -2440,11 +2273,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q25" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -2505,11 +2333,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q26" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -2570,11 +2393,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q27" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -2635,11 +2453,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q28" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -2700,11 +2513,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q29" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -2765,11 +2573,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q30" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -2830,11 +2633,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q31" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -2895,11 +2693,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q32" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -2960,11 +2753,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q33" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -3025,11 +2813,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q34" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -3090,11 +2873,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q35" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -3155,11 +2933,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q36" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -3220,11 +2993,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q37" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -3285,11 +3053,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q38" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -3350,11 +3113,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q39" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -3415,11 +3173,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q40" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -3480,11 +3233,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q41" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -3545,11 +3293,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q42" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
@@ -3610,11 +3353,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q43" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
@@ -3675,74 +3413,64 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q44" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="47" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>3.56.60.056.VIE.00.000</t>
         </is>
       </c>
-      <c r="B45" s="47" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp TU 24kV 22000/√3/110/√3V-15VA CCX 0,5 epoxy chân không</t>
         </is>
       </c>
-      <c r="C45" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D45" s="48" t="n">
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F45" s="49" t="n">
+      <c r="E45" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F45" s="4" t="n">
         <v>46063</v>
       </c>
-      <c r="G45" s="48" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>01.VH6.11.0001</t>
         </is>
       </c>
-      <c r="H45" s="48" t="n"/>
-      <c r="I45" s="47" t="inlineStr">
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập TU,  phục vụ SCL 2026 theo PGH:03.VH6.41.0004(02/02/2026)</t>
         </is>
       </c>
-      <c r="J45" s="50" t="n">
+      <c r="J45" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="K45" s="50" t="n">
+      <c r="K45" s="43" t="n">
         <v>9892914.33</v>
       </c>
-      <c r="L45" s="50" t="n">
+      <c r="L45" s="43" t="n">
         <v>29678743</v>
       </c>
-      <c r="M45" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="52" t="inlineStr">
+      <c r="M45" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q45" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -3805,11 +3533,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q46" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -3870,11 +3593,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q47" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -3935,11 +3653,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q48" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -4000,11 +3713,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q49" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -4065,11 +3773,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q50" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -4130,11 +3833,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q51" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -4195,11 +3893,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q52" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -4260,11 +3953,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q53" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -4325,11 +4013,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q54" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -4390,11 +4073,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q55" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -4455,11 +4133,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q56" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -4520,11 +4193,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q57" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -4585,11 +4253,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q58" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -4650,11 +4313,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q59" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -4715,11 +4373,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q60" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -4780,11 +4433,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q61" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -4845,11 +4493,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q62" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -4910,11 +4553,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q63" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -4975,11 +4613,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q64" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -5040,11 +4673,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q65" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -5105,11 +4733,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q66" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -5170,11 +4793,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q67" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -5235,11 +4853,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q68" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -5300,11 +4913,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q69" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -5365,11 +4973,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q70" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -5430,11 +5033,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q71" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -5495,11 +5093,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q72" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -5560,11 +5153,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q73" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
@@ -5625,11 +5213,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q74" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -5690,11 +5273,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q75" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -5755,11 +5333,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q76" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
@@ -5820,11 +5393,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q77" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
@@ -5885,11 +5453,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q78" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
@@ -5950,11 +5513,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q79" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -6015,11 +5573,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q80" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
@@ -6080,11 +5633,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q81" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -6145,11 +5693,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q82" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -6210,11 +5753,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q83" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
@@ -6275,11 +5813,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q84" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -6340,11 +5873,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q85" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
@@ -6405,11 +5933,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q86" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -6470,269 +5993,244 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q87" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="88">
-      <c r="A88" s="47" t="inlineStr">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>3.53.65.160.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B88" s="47" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 250-500/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C88" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D88" s="48" t="n">
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E88" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F88" s="49" t="n">
+      <c r="E88" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F88" s="4" t="n">
         <v>46105</v>
       </c>
-      <c r="G88" s="48" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H88" s="48" t="n"/>
-      <c r="I88" s="47" t="inlineStr">
+      <c r="H88" s="6" t="n"/>
+      <c r="I88" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J88" s="50" t="n">
+      <c r="J88" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="K88" s="50" t="n">
+      <c r="K88" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L88" s="50" t="n">
+      <c r="L88" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M88" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" s="52" t="inlineStr">
+      <c r="M88" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q88" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="89">
-      <c r="A89" s="47" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>3.53.65.145.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B89" s="47" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 20-40/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C89" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D89" s="48" t="n">
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E89" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F89" s="49" t="n">
+      <c r="E89" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F89" s="4" t="n">
         <v>46105</v>
       </c>
-      <c r="G89" s="48" t="inlineStr">
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H89" s="48" t="n"/>
-      <c r="I89" s="47" t="inlineStr">
+      <c r="H89" s="6" t="n"/>
+      <c r="I89" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J89" s="50" t="n">
+      <c r="J89" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K89" s="50" t="n">
+      <c r="K89" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L89" s="50" t="n">
+      <c r="L89" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M89" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" s="52" t="inlineStr">
+      <c r="M89" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q89" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="90">
-      <c r="A90" s="47" t="inlineStr">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>3.53.65.147.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B90" s="47" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 30-60/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C90" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D90" s="48" t="n">
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E90" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F90" s="49" t="n">
+      <c r="E90" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F90" s="4" t="n">
         <v>46105</v>
       </c>
-      <c r="G90" s="48" t="inlineStr">
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H90" s="48" t="n"/>
-      <c r="I90" s="47" t="inlineStr">
+      <c r="H90" s="6" t="n"/>
+      <c r="I90" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J90" s="50" t="n">
+      <c r="J90" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K90" s="50" t="n">
+      <c r="K90" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L90" s="50" t="n">
+      <c r="L90" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M90" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" s="52" t="inlineStr">
+      <c r="M90" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q90" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="91">
-      <c r="A91" s="47" t="inlineStr">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>3.53.65.025.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B91" s="47" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 25-50/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C91" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D91" s="48" t="n">
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E91" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F91" s="49" t="n">
+      <c r="E91" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F91" s="4" t="n">
         <v>46105</v>
       </c>
-      <c r="G91" s="48" t="inlineStr">
+      <c r="G91" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0016</t>
         </is>
       </c>
-      <c r="H91" s="48" t="n"/>
-      <c r="I91" s="47" t="inlineStr">
+      <c r="H91" s="6" t="n"/>
+      <c r="I91" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT SCL 2026</t>
         </is>
       </c>
-      <c r="J91" s="50" t="n">
+      <c r="J91" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="K91" s="50" t="n">
+      <c r="K91" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L91" s="50" t="n">
+      <c r="L91" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M91" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" s="52" t="inlineStr">
+      <c r="M91" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q91" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -6795,11 +6293,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q92" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -6860,11 +6353,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q93" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
@@ -6925,11 +6413,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q94" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
@@ -6990,11 +6473,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q95" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
@@ -7055,11 +6533,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q96" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
@@ -7120,11 +6593,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q97" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
@@ -7185,74 +6653,64 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q98" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="99">
-      <c r="A99" s="47" t="inlineStr">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>3.53.65.145.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B99" s="47" t="inlineStr">
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 20-40/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C99" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D99" s="48" t="n">
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E99" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F99" s="49" t="n">
+      <c r="E99" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F99" s="4" t="n">
         <v>46107</v>
       </c>
-      <c r="G99" s="48" t="inlineStr">
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>01.VH4.11.0039</t>
         </is>
       </c>
-      <c r="H99" s="48" t="n"/>
-      <c r="I99" s="47" t="inlineStr">
+      <c r="H99" s="6" t="n"/>
+      <c r="I99" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI TT thay SCL</t>
         </is>
       </c>
-      <c r="J99" s="50" t="n">
+      <c r="J99" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K99" s="50" t="n">
+      <c r="K99" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L99" s="50" t="n">
+      <c r="L99" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M99" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="52" t="inlineStr">
+      <c r="M99" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q99" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -7315,11 +6773,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q100" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
@@ -7380,11 +6833,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q101" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
@@ -7445,11 +6893,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q102" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
@@ -7510,11 +6953,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q103" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
@@ -7575,11 +7013,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q104" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
@@ -7640,11 +7073,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q105" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -7705,11 +7133,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q106" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
@@ -7770,11 +7193,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q107" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
@@ -7835,11 +7253,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q108" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
@@ -7900,11 +7313,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q109" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
@@ -7965,11 +7373,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q110" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
@@ -8030,11 +7433,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q111" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
@@ -8095,11 +7493,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q112" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
@@ -8160,11 +7553,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q113" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
@@ -8225,11 +7613,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q114" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
@@ -8290,11 +7673,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q115" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
@@ -8355,11 +7733,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q116" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
@@ -8420,11 +7793,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q117" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
@@ -8485,11 +7853,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q118" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
@@ -8550,11 +7913,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q119" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
@@ -8615,11 +7973,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q120" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
@@ -8680,11 +8033,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q121" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
@@ -8745,11 +8093,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q122" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
@@ -8810,11 +8153,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q123" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
@@ -8875,11 +8213,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q124" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
@@ -8940,11 +8273,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q125" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
@@ -9005,11 +8333,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q126" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
@@ -9070,11 +8393,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q127" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
@@ -9135,11 +8453,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q128" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
@@ -9200,11 +8513,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q129" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
@@ -9265,464 +8573,424 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q130" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="131">
-      <c r="A131" s="47" t="inlineStr">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>3.53.65.025.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B131" s="47" t="inlineStr">
+      <c r="B131" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 25-50/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C131" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D131" s="48" t="n">
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E131" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F131" s="49" t="n">
+      <c r="E131" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F131" s="4" t="n">
         <v>46122</v>
       </c>
-      <c r="G131" s="48" t="inlineStr">
+      <c r="G131" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H131" s="48" t="n"/>
-      <c r="I131" s="47" t="inlineStr">
+      <c r="H131" s="6" t="n"/>
+      <c r="I131" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J131" s="50" t="n">
+      <c r="J131" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="K131" s="50" t="n">
+      <c r="K131" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L131" s="50" t="n">
+      <c r="L131" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M131" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" s="52" t="inlineStr">
+      <c r="M131" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q131" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="132">
-      <c r="A132" s="47" t="inlineStr">
+      <c r="A132" s="10" t="inlineStr">
         <is>
           <t>3.53.65.160.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B132" s="47" t="inlineStr">
+      <c r="B132" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 250-500/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C132" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D132" s="48" t="n">
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E132" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F132" s="49" t="n">
+      <c r="E132" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F132" s="4" t="n">
         <v>46122</v>
       </c>
-      <c r="G132" s="48" t="inlineStr">
+      <c r="G132" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H132" s="48" t="n"/>
-      <c r="I132" s="47" t="inlineStr">
+      <c r="H132" s="6" t="n"/>
+      <c r="I132" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J132" s="50" t="n">
+      <c r="J132" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K132" s="50" t="n">
+      <c r="K132" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L132" s="50" t="n">
+      <c r="L132" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M132" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" s="52" t="inlineStr">
+      <c r="M132" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q132" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="133">
-      <c r="A133" s="47" t="inlineStr">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>3.53.65.145.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B133" s="47" t="inlineStr">
+      <c r="B133" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 20-40/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C133" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D133" s="48" t="n">
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E133" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F133" s="49" t="n">
+      <c r="E133" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F133" s="4" t="n">
         <v>46122</v>
       </c>
-      <c r="G133" s="48" t="inlineStr">
+      <c r="G133" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H133" s="48" t="n"/>
-      <c r="I133" s="47" t="inlineStr">
+      <c r="H133" s="6" t="n"/>
+      <c r="I133" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J133" s="50" t="n">
+      <c r="J133" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="K133" s="50" t="n">
+      <c r="K133" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L133" s="50" t="n">
+      <c r="L133" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="M133" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" s="52" t="inlineStr">
+      <c r="M133" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q133" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="134">
-      <c r="A134" s="47" t="inlineStr">
+      <c r="A134" s="10" t="inlineStr">
         <is>
           <t>3.53.65.013.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B134" s="47" t="inlineStr">
+      <c r="B134" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 10-20/5A</t>
         </is>
       </c>
-      <c r="C134" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D134" s="48" t="n">
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E134" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F134" s="49" t="n">
+      <c r="E134" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F134" s="4" t="n">
         <v>46122</v>
       </c>
-      <c r="G134" s="48" t="inlineStr">
+      <c r="G134" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H134" s="48" t="n"/>
-      <c r="I134" s="47" t="inlineStr">
+      <c r="H134" s="6" t="n"/>
+      <c r="I134" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J134" s="50" t="n">
+      <c r="J134" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="K134" s="50" t="n">
+      <c r="K134" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L134" s="50" t="n">
+      <c r="L134" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M134" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" s="52" t="inlineStr">
+      <c r="M134" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q134" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="135">
-      <c r="A135" s="47" t="inlineStr">
+      <c r="A135" s="10" t="inlineStr">
         <is>
           <t>3.53.65.015.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B135" s="47" t="inlineStr">
+      <c r="B135" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 15-30/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C135" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D135" s="48" t="n">
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E135" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F135" s="49" t="n">
+      <c r="E135" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F135" s="4" t="n">
         <v>46122</v>
       </c>
-      <c r="G135" s="48" t="inlineStr">
+      <c r="G135" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H135" s="48" t="n"/>
-      <c r="I135" s="47" t="inlineStr">
+      <c r="H135" s="6" t="n"/>
+      <c r="I135" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J135" s="50" t="n">
+      <c r="J135" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K135" s="50" t="n">
+      <c r="K135" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L135" s="50" t="n">
+      <c r="L135" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M135" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" s="52" t="inlineStr">
+      <c r="M135" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q135" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="136">
-      <c r="A136" s="47" t="inlineStr">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>3.53.65.148.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B136" s="47" t="inlineStr">
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 50-100/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C136" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D136" s="48" t="n">
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E136" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F136" s="49" t="n">
+      <c r="E136" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F136" s="4" t="n">
         <v>46122</v>
       </c>
-      <c r="G136" s="48" t="inlineStr">
+      <c r="G136" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H136" s="48" t="n"/>
-      <c r="I136" s="47" t="inlineStr">
+      <c r="H136" s="6" t="n"/>
+      <c r="I136" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J136" s="50" t="n">
+      <c r="J136" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K136" s="50" t="n">
+      <c r="K136" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L136" s="50" t="n">
+      <c r="L136" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M136" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" s="52" t="inlineStr">
+      <c r="M136" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q136" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="137">
-      <c r="A137" s="47" t="inlineStr">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>3.56.60.056.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B137" s="47" t="inlineStr">
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp TU 24kV 22000/√3/110/√3V-15VA CCX 0,5 epoxy chân không</t>
         </is>
       </c>
-      <c r="C137" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D137" s="48" t="n">
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E137" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F137" s="49" t="n">
+      <c r="E137" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F137" s="4" t="n">
         <v>46122</v>
       </c>
-      <c r="G137" s="48" t="inlineStr">
+      <c r="G137" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0025</t>
         </is>
       </c>
-      <c r="H137" s="48" t="n"/>
-      <c r="I137" s="47" t="inlineStr">
+      <c r="H137" s="6" t="n"/>
+      <c r="I137" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TI, TU SCL 2026</t>
         </is>
       </c>
-      <c r="J137" s="50" t="n">
+      <c r="J137" s="43" t="n">
         <v>9</v>
       </c>
-      <c r="K137" s="50" t="n">
+      <c r="K137" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L137" s="50" t="n">
+      <c r="L137" s="43" t="n">
         <v>9</v>
       </c>
-      <c r="M137" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" s="52" t="inlineStr">
+      <c r="M137" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q137" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -9785,11 +9053,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q138" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
@@ -9850,11 +9113,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q139" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
@@ -9915,11 +9173,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q140" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
@@ -9980,11 +9233,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q141" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
@@ -10045,11 +9293,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q142" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
@@ -10110,11 +9353,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q143" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
@@ -10175,11 +9413,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q144" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
@@ -10240,11 +9473,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q145" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
@@ -10305,74 +9533,64 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q146" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="147">
-      <c r="A147" s="47" t="inlineStr">
+      <c r="A147" s="10" t="inlineStr">
         <is>
           <t>3.42.80.118.VIE.00.000</t>
         </is>
       </c>
-      <c r="B147" s="47" t="inlineStr">
+      <c r="B147" s="10" t="inlineStr">
         <is>
           <t>SPC - Chống sét van (LA) 18kV  Polymer kèm phụ kiện ( Dòng rò 31 mm/kV )</t>
         </is>
       </c>
-      <c r="C147" s="48" t="inlineStr">
+      <c r="C147" s="3" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D147" s="48" t="n">
+      <c r="D147" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E147" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F147" s="49" t="n">
+      <c r="E147" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F147" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G147" s="48" t="inlineStr">
+      <c r="G147" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0029</t>
         </is>
       </c>
-      <c r="H147" s="48" t="n"/>
-      <c r="I147" s="47" t="inlineStr">
+      <c r="H147" s="6" t="n"/>
+      <c r="I147" s="9" t="inlineStr">
         <is>
           <t>24017 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J147" s="50" t="n">
+      <c r="J147" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="K147" s="50" t="n">
+      <c r="K147" s="43" t="n">
         <v>1148800</v>
       </c>
-      <c r="L147" s="50" t="n">
+      <c r="L147" s="43" t="n">
         <v>5744000</v>
       </c>
-      <c r="M147" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" s="52" t="inlineStr">
+      <c r="M147" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q147" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -10435,659 +9653,604 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q148" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="149">
-      <c r="A149" s="47" t="inlineStr">
+      <c r="A149" s="10" t="inlineStr">
         <is>
           <t>3.15.82.025.VIE.00.000</t>
         </is>
       </c>
-      <c r="B149" s="47" t="inlineStr">
+      <c r="B149" s="10" t="inlineStr">
         <is>
           <t>SPC - Cáp đồng bọc 24KV CX(CR) 25mm2</t>
         </is>
       </c>
-      <c r="C149" s="48" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="D149" s="48" t="n">
+      <c r="D149" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E149" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F149" s="49" t="n">
+      <c r="E149" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F149" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G149" s="48" t="inlineStr">
+      <c r="G149" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0032</t>
         </is>
       </c>
-      <c r="H149" s="48" t="n"/>
-      <c r="I149" s="47" t="inlineStr">
+      <c r="H149" s="6" t="n"/>
+      <c r="I149" s="9" t="inlineStr">
         <is>
           <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J149" s="50" t="n">
+      <c r="J149" s="43" t="n">
         <v>165</v>
       </c>
-      <c r="K149" s="50" t="n">
+      <c r="K149" s="43" t="n">
         <v>108950</v>
       </c>
-      <c r="L149" s="50" t="n">
+      <c r="L149" s="43" t="n">
         <v>17976750</v>
       </c>
-      <c r="M149" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N149" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P149" s="52" t="inlineStr">
+      <c r="M149" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q149" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="150">
-      <c r="A150" s="47" t="inlineStr">
+      <c r="A150" s="10" t="inlineStr">
         <is>
           <t>3.42.80.117.CHN.00.000</t>
         </is>
       </c>
-      <c r="B150" s="47" t="inlineStr">
+      <c r="B150" s="10" t="inlineStr">
         <is>
           <t>SPC - Chống sét van (LA) 18kv kèm phụ kiện (dòng rò &gt;= 25mm/kV)</t>
         </is>
       </c>
-      <c r="C150" s="48" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D150" s="48" t="n">
+      <c r="D150" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E150" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F150" s="49" t="n">
+      <c r="E150" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F150" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G150" s="48" t="inlineStr">
+      <c r="G150" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0031</t>
         </is>
       </c>
-      <c r="H150" s="48" t="n"/>
-      <c r="I150" s="47" t="inlineStr">
+      <c r="H150" s="6" t="n"/>
+      <c r="I150" s="9" t="inlineStr">
         <is>
           <t>25017 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J150" s="50" t="n">
+      <c r="J150" s="43" t="n">
         <v>12</v>
       </c>
-      <c r="K150" s="50" t="n">
+      <c r="K150" s="43" t="n">
         <v>1103000</v>
       </c>
-      <c r="L150" s="50" t="n">
+      <c r="L150" s="43" t="n">
         <v>13236000</v>
       </c>
-      <c r="M150" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N150" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P150" s="52" t="inlineStr">
+      <c r="M150" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q150" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="151">
-      <c r="A151" s="47" t="inlineStr">
+      <c r="A151" s="10" t="inlineStr">
         <is>
           <t>3.30.22.101.VIE.00.000</t>
         </is>
       </c>
-      <c r="B151" s="47" t="inlineStr">
+      <c r="B151" s="10" t="inlineStr">
         <is>
           <t>SPC - Cầu chì tự rơi (FCO) 15/27KV 100A Polymer</t>
         </is>
       </c>
-      <c r="C151" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D151" s="48" t="n">
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E151" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F151" s="49" t="n">
+      <c r="E151" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F151" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G151" s="48" t="inlineStr">
+      <c r="G151" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0031</t>
         </is>
       </c>
-      <c r="H151" s="48" t="n"/>
-      <c r="I151" s="47" t="inlineStr">
+      <c r="H151" s="6" t="n"/>
+      <c r="I151" s="9" t="inlineStr">
         <is>
           <t>25017 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J151" s="50" t="n">
+      <c r="J151" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K151" s="50" t="n">
+      <c r="K151" s="43" t="n">
         <v>1553286</v>
       </c>
-      <c r="L151" s="50" t="n">
+      <c r="L151" s="43" t="n">
         <v>1553286</v>
       </c>
-      <c r="M151" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N151" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O151" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" s="52" t="inlineStr">
+      <c r="M151" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" s="45" t="inlineStr">
+        <is>
+          <t>Hạ thế</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>4.90.80.400.VIE.00.000</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>SPC - Chụp cách điện polymer cho FCO (chụp trên+ chụp dưới)</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>46134</v>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>01.VH1.16.0032</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="n"/>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
+        </is>
+      </c>
+      <c r="J152" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K152" s="43" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L152" s="43" t="n">
+        <v>450000</v>
+      </c>
+      <c r="M152" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q151" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="47" t="inlineStr">
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>3.42.80.117.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>SPC - Chống sét van (LA) 18kv kèm phụ kiện (dòng rò &gt;= 25mm/kV)</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>46134</v>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>01.VH1.16.0036</t>
+        </is>
+      </c>
+      <c r="H153" s="6" t="n"/>
+      <c r="I153" s="9" t="inlineStr">
+        <is>
+          <t>25015 -SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
+        </is>
+      </c>
+      <c r="J153" s="43" t="n">
+        <v>12</v>
+      </c>
+      <c r="K153" s="43" t="n">
+        <v>1103000</v>
+      </c>
+      <c r="L153" s="43" t="n">
+        <v>13236000</v>
+      </c>
+      <c r="M153" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="45" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="inlineStr">
+        <is>
+          <t>3.42.80.118.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>SPC - Chống sét van (LA) 18kV  Polymer kèm phụ kiện ( Dòng rò 31 mm/kV )</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>46134</v>
+      </c>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>01.VH1.16.0032</t>
+        </is>
+      </c>
+      <c r="H154" s="6" t="n"/>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
+        </is>
+      </c>
+      <c r="J154" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="K154" s="43" t="n">
+        <v>1111000</v>
+      </c>
+      <c r="L154" s="43" t="n">
+        <v>12221000</v>
+      </c>
+      <c r="M154" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="45" t="inlineStr">
+        <is>
+          <t>Hạ thế</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>4.90.80.400.000.00.000</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>Chụp đầu cực FCO</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>46134</v>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>01.VH1.16.0033</t>
+        </is>
+      </c>
+      <c r="H155" s="6" t="n"/>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>24025 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
+        </is>
+      </c>
+      <c r="J155" s="43" t="n">
+        <v>81</v>
+      </c>
+      <c r="K155" s="43" t="n">
+        <v>157500</v>
+      </c>
+      <c r="L155" s="43" t="n">
+        <v>12757500</v>
+      </c>
+      <c r="M155" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="45" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="10" t="inlineStr">
+        <is>
+          <t>4.90.80.400.000.00.000</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>Chụp đầu cực FCO</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>46134</v>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>01.VH1.16.0033</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="n"/>
+      <c r="I156" s="9" t="inlineStr">
+        <is>
+          <t>24025 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
+        </is>
+      </c>
+      <c r="J156" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="K156" s="43" t="n">
+        <v>157500</v>
+      </c>
+      <c r="L156" s="43" t="n">
+        <v>472500</v>
+      </c>
+      <c r="M156" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" s="45" t="inlineStr">
+        <is>
+          <t>Trung thế</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="inlineStr">
         <is>
           <t>4.90.80.400.VIE.00.000</t>
         </is>
       </c>
-      <c r="B152" s="47" t="inlineStr">
+      <c r="B157" s="10" t="inlineStr">
         <is>
           <t>SPC - Chụp cách điện polymer cho FCO (chụp trên+ chụp dưới)</t>
         </is>
       </c>
-      <c r="C152" s="48" t="inlineStr">
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D152" s="48" t="n">
+      <c r="D157" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E152" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F152" s="49" t="n">
+      <c r="E157" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F157" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G152" s="48" t="inlineStr">
+      <c r="G157" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0032</t>
         </is>
       </c>
-      <c r="H152" s="48" t="n"/>
-      <c r="I152" s="47" t="inlineStr">
+      <c r="H157" s="6" t="n"/>
+      <c r="I157" s="9" t="inlineStr">
         <is>
           <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J152" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="K152" s="50" t="n">
-        <v>90000</v>
-      </c>
-      <c r="L152" s="50" t="n">
-        <v>450000</v>
-      </c>
-      <c r="M152" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N152" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O152" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P152" s="52" t="inlineStr">
+      <c r="J157" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="K157" s="43" t="n">
+        <v>82000</v>
+      </c>
+      <c r="L157" s="43" t="n">
+        <v>738000</v>
+      </c>
+      <c r="M157" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q152" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="47" t="inlineStr">
-        <is>
-          <t>3.42.80.117.CHN.00.000</t>
-        </is>
-      </c>
-      <c r="B153" s="47" t="inlineStr">
-        <is>
-          <t>SPC - Chống sét van (LA) 18kv kèm phụ kiện (dòng rò &gt;= 25mm/kV)</t>
-        </is>
-      </c>
-      <c r="C153" s="48" t="inlineStr">
-        <is>
-          <t>Bộ</t>
-        </is>
-      </c>
-      <c r="D153" s="48" t="n">
+    </row>
+    <row r="158">
+      <c r="A158" s="10" t="inlineStr">
+        <is>
+          <t>4.90.80.400.000.00.000</t>
+        </is>
+      </c>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>Chụp đầu cực FCO</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E153" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F153" s="49" t="n">
+      <c r="E158" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F158" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G153" s="48" t="inlineStr">
-        <is>
-          <t>01.VH1.16.0036</t>
-        </is>
-      </c>
-      <c r="H153" s="48" t="n"/>
-      <c r="I153" s="47" t="inlineStr">
-        <is>
-          <t>25015 -SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
-        </is>
-      </c>
-      <c r="J153" s="50" t="n">
-        <v>12</v>
-      </c>
-      <c r="K153" s="50" t="n">
-        <v>1103000</v>
-      </c>
-      <c r="L153" s="50" t="n">
-        <v>13236000</v>
-      </c>
-      <c r="M153" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N153" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O153" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P153" s="52" t="inlineStr">
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>01.VH1.16.0034</t>
+        </is>
+      </c>
+      <c r="H158" s="6" t="n"/>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>24026 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
+        </is>
+      </c>
+      <c r="J158" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K158" s="43" t="n">
+        <v>157500</v>
+      </c>
+      <c r="L158" s="43" t="n">
+        <v>157500</v>
+      </c>
+      <c r="M158" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q153" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="47" t="inlineStr">
-        <is>
-          <t>3.42.80.118.CHN.00.000</t>
-        </is>
-      </c>
-      <c r="B154" s="47" t="inlineStr">
-        <is>
-          <t>SPC - Chống sét van (LA) 18kV  Polymer kèm phụ kiện ( Dòng rò 31 mm/kV )</t>
-        </is>
-      </c>
-      <c r="C154" s="48" t="inlineStr">
-        <is>
-          <t>Bộ</t>
-        </is>
-      </c>
-      <c r="D154" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E154" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F154" s="49" t="n">
-        <v>46134</v>
-      </c>
-      <c r="G154" s="48" t="inlineStr">
-        <is>
-          <t>01.VH1.16.0032</t>
-        </is>
-      </c>
-      <c r="H154" s="48" t="n"/>
-      <c r="I154" s="47" t="inlineStr">
-        <is>
-          <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
-        </is>
-      </c>
-      <c r="J154" s="50" t="n">
-        <v>11</v>
-      </c>
-      <c r="K154" s="50" t="n">
-        <v>1111000</v>
-      </c>
-      <c r="L154" s="50" t="n">
-        <v>12221000</v>
-      </c>
-      <c r="M154" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N154" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" s="52" t="inlineStr">
-        <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q154" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="47" t="inlineStr">
-        <is>
-          <t>4.90.80.400.000.00.000</t>
-        </is>
-      </c>
-      <c r="B155" s="47" t="inlineStr">
-        <is>
-          <t>Chụp đầu cực FCO</t>
-        </is>
-      </c>
-      <c r="C155" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D155" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E155" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F155" s="49" t="n">
-        <v>46134</v>
-      </c>
-      <c r="G155" s="48" t="inlineStr">
-        <is>
-          <t>01.VH1.16.0033</t>
-        </is>
-      </c>
-      <c r="H155" s="48" t="n"/>
-      <c r="I155" s="47" t="inlineStr">
-        <is>
-          <t>24025 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
-        </is>
-      </c>
-      <c r="J155" s="50" t="n">
-        <v>81</v>
-      </c>
-      <c r="K155" s="50" t="n">
-        <v>157500</v>
-      </c>
-      <c r="L155" s="50" t="n">
-        <v>12757500</v>
-      </c>
-      <c r="M155" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N155" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O155" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P155" s="52" t="inlineStr">
-        <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q155" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="47" t="inlineStr">
-        <is>
-          <t>4.90.80.400.000.00.000</t>
-        </is>
-      </c>
-      <c r="B156" s="47" t="inlineStr">
-        <is>
-          <t>Chụp đầu cực FCO</t>
-        </is>
-      </c>
-      <c r="C156" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D156" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E156" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F156" s="49" t="n">
-        <v>46134</v>
-      </c>
-      <c r="G156" s="48" t="inlineStr">
-        <is>
-          <t>01.VH1.16.0033</t>
-        </is>
-      </c>
-      <c r="H156" s="48" t="n"/>
-      <c r="I156" s="47" t="inlineStr">
-        <is>
-          <t>24025 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
-        </is>
-      </c>
-      <c r="J156" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="K156" s="50" t="n">
-        <v>157500</v>
-      </c>
-      <c r="L156" s="50" t="n">
-        <v>472500</v>
-      </c>
-      <c r="M156" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N156" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O156" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P156" s="52" t="inlineStr">
-        <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q156" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="47" t="inlineStr">
-        <is>
-          <t>4.90.80.400.VIE.00.000</t>
-        </is>
-      </c>
-      <c r="B157" s="47" t="inlineStr">
-        <is>
-          <t>SPC - Chụp cách điện polymer cho FCO (chụp trên+ chụp dưới)</t>
-        </is>
-      </c>
-      <c r="C157" s="48" t="inlineStr">
-        <is>
-          <t>Bộ</t>
-        </is>
-      </c>
-      <c r="D157" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E157" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F157" s="49" t="n">
-        <v>46134</v>
-      </c>
-      <c r="G157" s="48" t="inlineStr">
-        <is>
-          <t>01.VH1.16.0032</t>
-        </is>
-      </c>
-      <c r="H157" s="48" t="n"/>
-      <c r="I157" s="47" t="inlineStr">
-        <is>
-          <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
-        </is>
-      </c>
-      <c r="J157" s="50" t="n">
-        <v>9</v>
-      </c>
-      <c r="K157" s="50" t="n">
-        <v>82000</v>
-      </c>
-      <c r="L157" s="50" t="n">
-        <v>738000</v>
-      </c>
-      <c r="M157" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N157" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O157" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P157" s="52" t="inlineStr">
-        <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q157" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="47" t="inlineStr">
-        <is>
-          <t>4.90.80.400.000.00.000</t>
-        </is>
-      </c>
-      <c r="B158" s="47" t="inlineStr">
-        <is>
-          <t>Chụp đầu cực FCO</t>
-        </is>
-      </c>
-      <c r="C158" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D158" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E158" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F158" s="49" t="n">
-        <v>46134</v>
-      </c>
-      <c r="G158" s="48" t="inlineStr">
-        <is>
-          <t>01.VH1.16.0034</t>
-        </is>
-      </c>
-      <c r="H158" s="48" t="n"/>
-      <c r="I158" s="47" t="inlineStr">
-        <is>
-          <t>24026 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
-        </is>
-      </c>
-      <c r="J158" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K158" s="50" t="n">
-        <v>157500</v>
-      </c>
-      <c r="L158" s="50" t="n">
-        <v>157500</v>
-      </c>
-      <c r="M158" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N158" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P158" s="52" t="inlineStr">
-        <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q158" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -11150,334 +10313,304 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q159" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="160">
-      <c r="A160" s="47" t="inlineStr">
+      <c r="A160" s="10" t="inlineStr">
         <is>
           <t>3.42.80.117.CHN.00.000</t>
         </is>
       </c>
-      <c r="B160" s="47" t="inlineStr">
+      <c r="B160" s="10" t="inlineStr">
         <is>
           <t>SPC - Chống sét van (LA) 18kv kèm phụ kiện (dòng rò &gt;= 25mm/kV)</t>
         </is>
       </c>
-      <c r="C160" s="48" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D160" s="48" t="n">
+      <c r="D160" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E160" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F160" s="49" t="n">
+      <c r="E160" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F160" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G160" s="48" t="inlineStr">
+      <c r="G160" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0035</t>
         </is>
       </c>
-      <c r="H160" s="48" t="n"/>
-      <c r="I160" s="47" t="inlineStr">
+      <c r="H160" s="6" t="n"/>
+      <c r="I160" s="9" t="inlineStr">
         <is>
           <t>25014 -SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J160" s="50" t="n">
+      <c r="J160" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="K160" s="50" t="n">
+      <c r="K160" s="43" t="n">
         <v>1103000</v>
       </c>
-      <c r="L160" s="50" t="n">
+      <c r="L160" s="43" t="n">
         <v>19854000</v>
       </c>
-      <c r="M160" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N160" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O160" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" s="52" t="inlineStr">
+      <c r="M160" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q160" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="161">
-      <c r="A161" s="47" t="inlineStr">
+      <c r="A161" s="10" t="inlineStr">
         <is>
           <t>4.90.80.400.000.00.000</t>
         </is>
       </c>
-      <c r="B161" s="47" t="inlineStr">
+      <c r="B161" s="10" t="inlineStr">
         <is>
           <t>Chụp đầu cực FCO</t>
         </is>
       </c>
-      <c r="C161" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D161" s="48" t="n">
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E161" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F161" s="49" t="n">
+      <c r="E161" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F161" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G161" s="48" t="inlineStr">
+      <c r="G161" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0030</t>
         </is>
       </c>
-      <c r="H161" s="48" t="n"/>
-      <c r="I161" s="47" t="inlineStr">
+      <c r="H161" s="6" t="n"/>
+      <c r="I161" s="9" t="inlineStr">
         <is>
           <t>24028 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J161" s="50" t="n">
+      <c r="J161" s="43" t="n">
         <v>222</v>
       </c>
-      <c r="K161" s="50" t="n">
+      <c r="K161" s="43" t="n">
         <v>157500</v>
       </c>
-      <c r="L161" s="50" t="n">
+      <c r="L161" s="43" t="n">
         <v>34965000</v>
       </c>
-      <c r="M161" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N161" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O161" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" s="52" t="inlineStr">
+      <c r="M161" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q161" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="162">
-      <c r="A162" s="47" t="inlineStr">
+      <c r="A162" s="10" t="inlineStr">
         <is>
           <t>3.15.82.025.VIE.00.000</t>
         </is>
       </c>
-      <c r="B162" s="47" t="inlineStr">
+      <c r="B162" s="10" t="inlineStr">
         <is>
           <t>SPC - Cáp đồng bọc 24KV CX(CR) 25mm2</t>
         </is>
       </c>
-      <c r="C162" s="48" t="inlineStr">
+      <c r="C162" s="3" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="D162" s="48" t="n">
+      <c r="D162" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E162" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F162" s="49" t="n">
+      <c r="E162" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F162" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G162" s="48" t="inlineStr">
+      <c r="G162" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0030</t>
         </is>
       </c>
-      <c r="H162" s="48" t="n"/>
-      <c r="I162" s="47" t="inlineStr">
+      <c r="H162" s="6" t="n"/>
+      <c r="I162" s="9" t="inlineStr">
         <is>
           <t>24028 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J162" s="50" t="n">
+      <c r="J162" s="43" t="n">
         <v>57</v>
       </c>
-      <c r="K162" s="50" t="n">
+      <c r="K162" s="43" t="n">
         <v>101800</v>
       </c>
-      <c r="L162" s="50" t="n">
+      <c r="L162" s="43" t="n">
         <v>5802600</v>
       </c>
-      <c r="M162" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N162" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O162" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P162" s="52" t="inlineStr">
+      <c r="M162" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q162" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="163">
-      <c r="A163" s="47" t="inlineStr">
+      <c r="A163" s="10" t="inlineStr">
         <is>
           <t>3.30.22.121.VIE.00.000</t>
         </is>
       </c>
-      <c r="B163" s="47" t="inlineStr">
+      <c r="B163" s="10" t="inlineStr">
         <is>
           <t>SPC - FCO 22kV-100A-Polyme kèm phụ kiện (dòng rò &gt;= 31mm/kV)</t>
         </is>
       </c>
-      <c r="C163" s="48" t="inlineStr">
+      <c r="C163" s="3" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D163" s="48" t="n">
+      <c r="D163" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E163" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F163" s="49" t="n">
+      <c r="E163" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F163" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G163" s="48" t="inlineStr">
+      <c r="G163" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0029</t>
         </is>
       </c>
-      <c r="H163" s="48" t="n"/>
-      <c r="I163" s="47" t="inlineStr">
+      <c r="H163" s="6" t="n"/>
+      <c r="I163" s="9" t="inlineStr">
         <is>
           <t>24017 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J163" s="50" t="n">
+      <c r="J163" s="43" t="n">
         <v>26</v>
       </c>
-      <c r="K163" s="50" t="n">
+      <c r="K163" s="43" t="n">
         <v>1338750</v>
       </c>
-      <c r="L163" s="50" t="n">
+      <c r="L163" s="43" t="n">
         <v>34807500</v>
       </c>
-      <c r="M163" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N163" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O163" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" s="52" t="inlineStr">
+      <c r="M163" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q163" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="164">
-      <c r="A164" s="47" t="inlineStr">
+      <c r="A164" s="10" t="inlineStr">
         <is>
           <t>3.42.80.118.CHN.00.000</t>
         </is>
       </c>
-      <c r="B164" s="47" t="inlineStr">
+      <c r="B164" s="10" t="inlineStr">
         <is>
           <t>SPC - Chống sét van (LA) 18kV  Polymer kèm phụ kiện ( Dòng rò 31 mm/kV )</t>
         </is>
       </c>
-      <c r="C164" s="48" t="inlineStr">
+      <c r="C164" s="3" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D164" s="48" t="n">
+      <c r="D164" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E164" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F164" s="49" t="n">
+      <c r="E164" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F164" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G164" s="48" t="inlineStr">
+      <c r="G164" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0029</t>
         </is>
       </c>
-      <c r="H164" s="48" t="n"/>
-      <c r="I164" s="47" t="inlineStr">
+      <c r="H164" s="6" t="n"/>
+      <c r="I164" s="9" t="inlineStr">
         <is>
           <t>24017 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J164" s="50" t="n">
+      <c r="J164" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="K164" s="50" t="n">
+      <c r="K164" s="43" t="n">
         <v>1263800</v>
       </c>
-      <c r="L164" s="50" t="n">
+      <c r="L164" s="43" t="n">
         <v>5055200</v>
       </c>
-      <c r="M164" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N164" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O164" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" s="52" t="inlineStr">
-        <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q164" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
+      <c r="M164" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" s="45" t="inlineStr">
+        <is>
+          <t>Hạ thế</t>
         </is>
       </c>
     </row>
@@ -11540,11 +10673,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q165" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" s="10" t="inlineStr">
@@ -11605,139 +10733,124 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q166" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="167">
-      <c r="A167" s="47" t="inlineStr">
+      <c r="A167" s="10" t="inlineStr">
         <is>
           <t>4.90.80.400.000.00.000</t>
         </is>
       </c>
-      <c r="B167" s="47" t="inlineStr">
+      <c r="B167" s="10" t="inlineStr">
         <is>
           <t>Chụp đầu cực FCO</t>
         </is>
       </c>
-      <c r="C167" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D167" s="48" t="n">
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E167" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F167" s="49" t="n">
+      <c r="E167" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F167" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G167" s="48" t="inlineStr">
+      <c r="G167" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0034</t>
         </is>
       </c>
-      <c r="H167" s="48" t="n"/>
-      <c r="I167" s="47" t="inlineStr">
+      <c r="H167" s="6" t="n"/>
+      <c r="I167" s="9" t="inlineStr">
         <is>
           <t>24026 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J167" s="50" t="n">
+      <c r="J167" s="43" t="n">
         <v>28</v>
       </c>
-      <c r="K167" s="50" t="n">
+      <c r="K167" s="43" t="n">
         <v>157500</v>
       </c>
-      <c r="L167" s="50" t="n">
+      <c r="L167" s="43" t="n">
         <v>4410000</v>
       </c>
-      <c r="M167" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N167" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O167" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" s="52" t="inlineStr">
+      <c r="M167" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q167" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="168">
-      <c r="A168" s="47" t="inlineStr">
+      <c r="A168" s="10" t="inlineStr">
         <is>
           <t>4.90.80.400.VIE.00.000</t>
         </is>
       </c>
-      <c r="B168" s="47" t="inlineStr">
+      <c r="B168" s="10" t="inlineStr">
         <is>
           <t>SPC - Chụp cách điện polymer cho FCO (chụp trên+ chụp dưới)</t>
         </is>
       </c>
-      <c r="C168" s="48" t="inlineStr">
+      <c r="C168" s="3" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="D168" s="48" t="n">
+      <c r="D168" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E168" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F168" s="49" t="n">
+      <c r="E168" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F168" s="4" t="n">
         <v>46134</v>
       </c>
-      <c r="G168" s="48" t="inlineStr">
+      <c r="G168" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0032</t>
         </is>
       </c>
-      <c r="H168" s="48" t="n"/>
-      <c r="I168" s="47" t="inlineStr">
+      <c r="H168" s="6" t="n"/>
+      <c r="I168" s="9" t="inlineStr">
         <is>
           <t>24029 SX Nhập vật tư điều chuyển từ ĐTXD về SXKD cấp cho công trình SCL năm 2026</t>
         </is>
       </c>
-      <c r="J168" s="50" t="n">
+      <c r="J168" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="K168" s="50" t="n">
+      <c r="K168" s="43" t="n">
         <v>90000</v>
       </c>
-      <c r="L168" s="50" t="n">
+      <c r="L168" s="43" t="n">
         <v>360000</v>
       </c>
-      <c r="M168" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N168" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O168" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" s="52" t="inlineStr">
+      <c r="M168" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q168" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -11800,11 +10913,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q169" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" s="10" t="inlineStr">
@@ -11865,11 +10973,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q170" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
@@ -11930,11 +11033,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q171" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" s="10" t="inlineStr">
@@ -11995,11 +11093,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q172" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
@@ -12060,11 +11153,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q173" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" s="10" t="inlineStr">
@@ -12125,11 +11213,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q174" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" s="10" t="inlineStr">
@@ -12190,11 +11273,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q175" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" s="10" t="inlineStr">
@@ -12255,74 +11333,64 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q176" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="177">
-      <c r="A177" s="47" t="inlineStr">
+      <c r="A177" s="10" t="inlineStr">
         <is>
           <t>3.56.60.121.000.00.AXX</t>
         </is>
       </c>
-      <c r="B177" s="47" t="inlineStr">
+      <c r="B177" s="10" t="inlineStr">
         <is>
           <t>Biến điện áp 22(15):V3/0,1:V3 kV - 15VA</t>
         </is>
       </c>
-      <c r="C177" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D177" s="48" t="n">
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E177" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F177" s="49" t="n">
+      <c r="E177" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F177" s="4" t="n">
         <v>46136</v>
       </c>
-      <c r="G177" s="48" t="inlineStr">
+      <c r="G177" s="5" t="inlineStr">
         <is>
           <t>01.VH4.11.0059</t>
         </is>
       </c>
-      <c r="H177" s="48" t="n"/>
-      <c r="I177" s="47" t="inlineStr">
+      <c r="H177" s="6" t="n"/>
+      <c r="I177" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập lại  TU, TI SCL T4-2026 03.VH4.41.0026</t>
         </is>
       </c>
-      <c r="J177" s="50" t="n">
+      <c r="J177" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K177" s="50" t="n">
+      <c r="K177" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L177" s="50" t="n">
+      <c r="L177" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M177" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N177" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O177" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P177" s="52" t="inlineStr">
+      <c r="M177" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q177" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -12385,11 +11453,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q178" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" s="10" t="inlineStr">
@@ -12450,204 +11513,184 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q179" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="180">
-      <c r="A180" s="47" t="inlineStr">
+      <c r="A180" s="10" t="inlineStr">
         <is>
           <t>3.53.65.148.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B180" s="47" t="inlineStr">
+      <c r="B180" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 50-100/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C180" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D180" s="48" t="n">
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E180" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F180" s="49" t="n">
+      <c r="E180" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F180" s="4" t="n">
         <v>46140</v>
       </c>
-      <c r="G180" s="48" t="inlineStr">
+      <c r="G180" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H180" s="48" t="n"/>
-      <c r="I180" s="47" t="inlineStr">
+      <c r="H180" s="6" t="n"/>
+      <c r="I180" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J180" s="50" t="n">
+      <c r="J180" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="K180" s="50" t="n">
+      <c r="K180" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L180" s="50" t="n">
+      <c r="L180" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M180" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O180" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" s="52" t="inlineStr">
+      <c r="M180" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q180" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="181">
-      <c r="A181" s="47" t="inlineStr">
+      <c r="A181" s="10" t="inlineStr">
         <is>
           <t>3.56.60.032.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B181" s="47" t="inlineStr">
+      <c r="B181" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp (TU 1P 12000/120V-15VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C181" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D181" s="48" t="n">
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E181" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F181" s="49" t="n">
+      <c r="E181" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F181" s="4" t="n">
         <v>46140</v>
       </c>
-      <c r="G181" s="48" t="inlineStr">
+      <c r="G181" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H181" s="48" t="n"/>
-      <c r="I181" s="47" t="inlineStr">
+      <c r="H181" s="6" t="n"/>
+      <c r="I181" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J181" s="50" t="n">
+      <c r="J181" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="K181" s="50" t="n">
+      <c r="K181" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L181" s="50" t="n">
+      <c r="L181" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="M181" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O181" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P181" s="52" t="inlineStr">
+      <c r="M181" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q181" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="182">
-      <c r="A182" s="47" t="inlineStr">
+      <c r="A182" s="10" t="inlineStr">
         <is>
           <t>3.53.65.015.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B182" s="47" t="inlineStr">
+      <c r="B182" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 15-30/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C182" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D182" s="48" t="n">
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E182" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F182" s="49" t="n">
+      <c r="E182" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F182" s="4" t="n">
         <v>46140</v>
       </c>
-      <c r="G182" s="48" t="inlineStr">
+      <c r="G182" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H182" s="48" t="n"/>
-      <c r="I182" s="47" t="inlineStr">
+      <c r="H182" s="6" t="n"/>
+      <c r="I182" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J182" s="50" t="n">
+      <c r="J182" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K182" s="50" t="n">
+      <c r="K182" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L182" s="50" t="n">
+      <c r="L182" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M182" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O182" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" s="52" t="inlineStr">
+      <c r="M182" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q182" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -12710,11 +11753,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q183" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" s="10" t="inlineStr">
@@ -12775,11 +11813,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q184" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" s="10" t="inlineStr">
@@ -12840,11 +11873,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q185" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" s="10" t="inlineStr">
@@ -12905,11 +11933,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q186" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" s="10" t="inlineStr">
@@ -12970,74 +11993,64 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q187" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="188">
-      <c r="A188" s="47" t="inlineStr">
+      <c r="A188" s="10" t="inlineStr">
         <is>
           <t>3.53.65.152.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B188" s="47" t="inlineStr">
+      <c r="B188" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24KV 150-300/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C188" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D188" s="48" t="n">
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E188" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F188" s="49" t="n">
+      <c r="E188" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F188" s="4" t="n">
         <v>46140</v>
       </c>
-      <c r="G188" s="48" t="inlineStr">
+      <c r="G188" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0038</t>
         </is>
       </c>
-      <c r="H188" s="48" t="n"/>
-      <c r="I188" s="47" t="inlineStr">
+      <c r="H188" s="6" t="n"/>
+      <c r="I188" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J188" s="50" t="n">
+      <c r="J188" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K188" s="50" t="n">
+      <c r="K188" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L188" s="50" t="n">
+      <c r="L188" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M188" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N188" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O188" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P188" s="52" t="inlineStr">
+      <c r="M188" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q188" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -13100,11 +12113,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q189" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
@@ -13165,11 +12173,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q190" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" s="10" t="inlineStr">
@@ -13230,11 +12233,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q191" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" s="10" t="inlineStr">
@@ -13295,11 +12293,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q192" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" s="10" t="inlineStr">
@@ -13360,11 +12353,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q193" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" s="10" t="inlineStr">
@@ -13425,11 +12413,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q194" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" s="10" t="inlineStr">
@@ -13490,11 +12473,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q195" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" s="10" t="inlineStr">
@@ -13555,11 +12533,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q196" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" s="10" t="inlineStr">
@@ -13620,11 +12593,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q197" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" s="10" t="inlineStr">
@@ -13685,11 +12653,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q198" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" s="10" t="inlineStr">
@@ -13750,11 +12713,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q199" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" s="10" t="inlineStr">
@@ -13815,74 +12773,64 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q200" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="201">
-      <c r="A201" s="47" t="inlineStr">
+      <c r="A201" s="10" t="inlineStr">
         <is>
           <t>3.56.60.032.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B201" s="47" t="inlineStr">
+      <c r="B201" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp (TU 1P 12000/120V-15VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C201" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D201" s="48" t="n">
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E201" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F201" s="49" t="n">
+      <c r="E201" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F201" s="4" t="n">
         <v>46140</v>
       </c>
-      <c r="G201" s="48" t="inlineStr">
+      <c r="G201" s="5" t="inlineStr">
         <is>
           <t>01.VH8.12.0037</t>
         </is>
       </c>
-      <c r="H201" s="48" t="n"/>
-      <c r="I201" s="47" t="inlineStr">
+      <c r="H201" s="6" t="n"/>
+      <c r="I201" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J201" s="50" t="n">
+      <c r="J201" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K201" s="50" t="n">
+      <c r="K201" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L201" s="50" t="n">
+      <c r="L201" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M201" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N201" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O201" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P201" s="52" t="inlineStr">
+      <c r="M201" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q201" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -13945,11 +12893,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q202" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" s="10" t="inlineStr">
@@ -14010,11 +12953,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q203" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" s="10" t="inlineStr">
@@ -14075,11 +13013,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q204" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" s="10" t="inlineStr">
@@ -14140,74 +13073,64 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q205" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="206">
-      <c r="A206" s="47" t="inlineStr">
+      <c r="A206" s="10" t="inlineStr">
         <is>
           <t>3.53.65.015.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B206" s="47" t="inlineStr">
+      <c r="B206" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (TI) 24kV 15-30/5A 10VA epoxy chân không</t>
         </is>
       </c>
-      <c r="C206" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D206" s="48" t="n">
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E206" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F206" s="49" t="n">
+      <c r="E206" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F206" s="4" t="n">
         <v>46140</v>
       </c>
-      <c r="G206" s="48" t="inlineStr">
+      <c r="G206" s="5" t="inlineStr">
         <is>
           <t>01.VH8.12.0037</t>
         </is>
       </c>
-      <c r="H206" s="48" t="n"/>
-      <c r="I206" s="47" t="inlineStr">
+      <c r="H206" s="6" t="n"/>
+      <c r="I206" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 nhập thu hồi TI, TU SCL</t>
         </is>
       </c>
-      <c r="J206" s="50" t="n">
+      <c r="J206" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K206" s="50" t="n">
+      <c r="K206" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L206" s="50" t="n">
+      <c r="L206" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M206" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N206" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O206" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P206" s="52" t="inlineStr">
+      <c r="M206" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q206" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -14270,11 +13193,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q207" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" s="10" t="inlineStr">
@@ -14335,11 +13253,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q208" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" s="10" t="inlineStr">
@@ -14400,11 +13313,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q209" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" s="10" t="inlineStr">
@@ -14465,11 +13373,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q210" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" s="10" t="inlineStr">
@@ -14530,11 +13433,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q211" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" s="10" t="inlineStr">
@@ -14595,11 +13493,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q212" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" s="10" t="inlineStr">
@@ -14660,11 +13553,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q213" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" s="10" t="inlineStr">
@@ -14725,11 +13613,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q214" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" s="10" t="inlineStr">
@@ -14790,11 +13673,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q215" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" s="10" t="inlineStr">
@@ -14855,11 +13733,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q216" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" s="10" t="inlineStr">
@@ -14920,11 +13793,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q217" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" s="10" t="inlineStr">
@@ -14985,11 +13853,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q218" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" s="10" t="inlineStr">
@@ -15050,11 +13913,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q219" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" s="10" t="inlineStr">
@@ -15115,11 +13973,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q220" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" s="10" t="inlineStr">
@@ -15180,11 +14033,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q221" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" s="10" t="inlineStr">
@@ -15245,11 +14093,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q222" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" s="10" t="inlineStr">
@@ -15310,11 +14153,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q223" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" s="10" t="inlineStr">
@@ -15375,11 +14213,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q224" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" s="10" t="inlineStr">
@@ -15440,11 +14273,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q225" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" s="10" t="inlineStr">
@@ -15505,11 +14333,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q226" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" s="10" t="inlineStr">
@@ -15570,11 +14393,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q227" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" s="10" t="inlineStr">
@@ -15635,11 +14453,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q228" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
@@ -15700,11 +14513,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q229" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
@@ -15765,11 +14573,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q230" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
@@ -15830,11 +14633,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q231" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" s="10" t="inlineStr">
@@ -15895,11 +14693,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q232" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" s="10" t="inlineStr">
@@ -15960,11 +14753,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q233" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" s="10" t="inlineStr">
@@ -16025,11 +14813,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q234" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" s="10" t="inlineStr">
@@ -16090,11 +14873,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q235" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" s="10" t="inlineStr">
@@ -16155,11 +14933,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q236" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" s="10" t="inlineStr">
@@ -16220,11 +14993,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q237" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" s="10" t="inlineStr">
@@ -16285,11 +15053,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q238" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" s="10" t="inlineStr">
@@ -16350,11 +15113,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q239" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" s="10" t="inlineStr">
@@ -16415,11 +15173,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q240" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" s="10" t="inlineStr">
@@ -16480,11 +15233,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q241" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" s="10" t="inlineStr">
@@ -16545,11 +15293,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q242" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" s="10" t="inlineStr">
@@ -16610,74 +15353,64 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q243" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="244">
-      <c r="A244" s="47" t="inlineStr">
+      <c r="A244" s="10" t="inlineStr">
         <is>
           <t>3.53.05.203.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B244" s="47" t="inlineStr">
+      <c r="B244" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 200/5A</t>
         </is>
       </c>
-      <c r="C244" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D244" s="48" t="n">
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E244" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F244" s="49" t="n">
+      <c r="E244" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F244" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G244" s="48" t="inlineStr">
+      <c r="G244" s="5" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H244" s="48" t="n"/>
-      <c r="I244" s="47" t="inlineStr">
+      <c r="H244" s="6" t="n"/>
+      <c r="I244" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J244" s="50" t="n">
+      <c r="J244" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="K244" s="50" t="n">
+      <c r="K244" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L244" s="50" t="n">
+      <c r="L244" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="M244" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N244" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O244" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P244" s="52" t="inlineStr">
+      <c r="M244" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
-        </is>
-      </c>
-      <c r="Q244" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -16740,11 +15473,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q245" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" s="10" t="inlineStr">
@@ -16805,11 +15533,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q246" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" s="10" t="inlineStr">
@@ -16870,11 +15593,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q247" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" s="10" t="inlineStr">
@@ -16935,11 +15653,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q248" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" s="10" t="inlineStr">
@@ -17000,11 +15713,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q249" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" s="10" t="inlineStr">
@@ -17065,11 +15773,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q250" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" s="10" t="inlineStr">
@@ -17130,11 +15833,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q251" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" s="10" t="inlineStr">
@@ -17195,11 +15893,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q252" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" s="10" t="inlineStr">
@@ -17260,11 +15953,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q253" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" s="10" t="inlineStr">
@@ -17325,11 +16013,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q254" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" s="10" t="inlineStr">
@@ -17390,11 +16073,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q255" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" s="10" t="inlineStr">
@@ -17455,11 +16133,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q256" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" s="10" t="inlineStr">
@@ -17520,11 +16193,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q257" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" s="10" t="inlineStr">
@@ -17585,11 +16253,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q258" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" s="10" t="inlineStr">
@@ -17650,11 +16313,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q259" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" s="10" t="inlineStr">
@@ -17715,11 +16373,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q260" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" s="10" t="inlineStr">
@@ -17777,12 +16430,7 @@
       </c>
       <c r="P261" s="45" t="inlineStr">
         <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q261" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
+          <t>Hạ thế</t>
         </is>
       </c>
     </row>
@@ -17845,139 +16493,124 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q262" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="263">
-      <c r="A263" s="47" t="inlineStr">
+      <c r="A263" s="10" t="inlineStr">
         <is>
           <t>3.53.05.150.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B263" s="47" t="inlineStr">
+      <c r="B263" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 150/5A 5VA CCX 0,5</t>
         </is>
       </c>
-      <c r="C263" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D263" s="48" t="n">
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E263" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F263" s="49" t="n">
+      <c r="E263" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F263" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G263" s="48" t="inlineStr">
+      <c r="G263" s="5" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H263" s="48" t="n"/>
-      <c r="I263" s="47" t="inlineStr">
+      <c r="H263" s="6" t="n"/>
+      <c r="I263" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J263" s="50" t="n">
+      <c r="J263" s="43" t="n">
         <v>25</v>
       </c>
-      <c r="K263" s="50" t="n">
+      <c r="K263" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L263" s="50" t="n">
+      <c r="L263" s="43" t="n">
         <v>25</v>
       </c>
-      <c r="M263" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N263" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O263" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P263" s="52" t="inlineStr">
+      <c r="M263" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N263" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q263" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="264">
-      <c r="A264" s="47" t="inlineStr">
+      <c r="A264" s="10" t="inlineStr">
         <is>
           <t>3.53.05.314.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B264" s="47" t="inlineStr">
+      <c r="B264" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 300/5A</t>
         </is>
       </c>
-      <c r="C264" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D264" s="48" t="n">
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E264" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F264" s="49" t="n">
+      <c r="E264" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F264" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G264" s="48" t="inlineStr">
+      <c r="G264" s="5" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H264" s="48" t="n"/>
-      <c r="I264" s="47" t="inlineStr">
+      <c r="H264" s="6" t="n"/>
+      <c r="I264" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J264" s="50" t="n">
+      <c r="J264" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="K264" s="50" t="n">
+      <c r="K264" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L264" s="50" t="n">
+      <c r="L264" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="M264" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N264" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O264" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P264" s="52" t="inlineStr">
+      <c r="M264" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
-        </is>
-      </c>
-      <c r="Q264" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -18040,11 +16673,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q265" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" s="10" t="inlineStr">
@@ -18105,11 +16733,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q266" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" s="10" t="inlineStr">
@@ -18167,12 +16790,7 @@
       </c>
       <c r="P267" s="45" t="inlineStr">
         <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q267" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
+          <t>Hạ thế</t>
         </is>
       </c>
     </row>
@@ -18235,11 +16853,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q268" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" s="10" t="inlineStr">
@@ -18300,11 +16913,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q269" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" s="10" t="inlineStr">
@@ -18365,11 +16973,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q270" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" s="10" t="inlineStr">
@@ -18430,594 +17033,544 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q271" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="272">
-      <c r="A272" s="47" t="inlineStr">
+      <c r="A272" s="10" t="inlineStr">
         <is>
           <t>3.53.05.105.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B272" s="47" t="inlineStr">
+      <c r="B272" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 100/5A</t>
         </is>
       </c>
-      <c r="C272" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D272" s="48" t="n">
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E272" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F272" s="49" t="n">
+      <c r="E272" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F272" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G272" s="48" t="inlineStr">
+      <c r="G272" s="5" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H272" s="48" t="n"/>
-      <c r="I272" s="47" t="inlineStr">
+      <c r="H272" s="6" t="n"/>
+      <c r="I272" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J272" s="50" t="n">
+      <c r="J272" s="43" t="n">
         <v>11</v>
       </c>
-      <c r="K272" s="50" t="n">
+      <c r="K272" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L272" s="50" t="n">
+      <c r="L272" s="43" t="n">
         <v>11</v>
       </c>
-      <c r="M272" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N272" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O272" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P272" s="52" t="inlineStr">
+      <c r="M272" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N272" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P272" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q272" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="273">
-      <c r="A273" s="47" t="inlineStr">
+      <c r="A273" s="10" t="inlineStr">
         <is>
           <t>3.53.05.150.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B273" s="47" t="inlineStr">
+      <c r="B273" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 150/5A 5VA CCX 0,5</t>
         </is>
       </c>
-      <c r="C273" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D273" s="48" t="n">
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E273" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F273" s="49" t="n">
+      <c r="E273" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F273" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G273" s="48" t="inlineStr">
+      <c r="G273" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H273" s="48" t="n"/>
-      <c r="I273" s="47" t="inlineStr">
+      <c r="H273" s="6" t="n"/>
+      <c r="I273" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J273" s="50" t="n">
+      <c r="J273" s="43" t="n">
         <v>15</v>
       </c>
-      <c r="K273" s="50" t="n">
+      <c r="K273" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L273" s="50" t="n">
+      <c r="L273" s="43" t="n">
         <v>15</v>
       </c>
-      <c r="M273" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N273" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O273" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P273" s="52" t="inlineStr">
+      <c r="M273" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N273" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q273" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="274">
-      <c r="A274" s="47" t="inlineStr">
+      <c r="A274" s="10" t="inlineStr">
         <is>
           <t>3.53.05.320.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B274" s="47" t="inlineStr">
+      <c r="B274" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 800/5A</t>
         </is>
       </c>
-      <c r="C274" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D274" s="48" t="n">
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E274" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F274" s="49" t="n">
+      <c r="E274" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F274" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G274" s="48" t="inlineStr">
+      <c r="G274" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H274" s="48" t="n"/>
-      <c r="I274" s="47" t="inlineStr">
+      <c r="H274" s="6" t="n"/>
+      <c r="I274" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J274" s="50" t="n">
+      <c r="J274" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="K274" s="50" t="n">
+      <c r="K274" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L274" s="50" t="n">
+      <c r="L274" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M274" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N274" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O274" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P274" s="52" t="inlineStr">
+      <c r="M274" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N274" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q274" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="275">
-      <c r="A275" s="47" t="inlineStr">
+      <c r="A275" s="10" t="inlineStr">
         <is>
           <t>3.53.05.334.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B275" s="47" t="inlineStr">
+      <c r="B275" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 1000/5A-5VA-CCX 0,5</t>
         </is>
       </c>
-      <c r="C275" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D275" s="48" t="n">
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E275" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F275" s="49" t="n">
+      <c r="E275" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F275" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G275" s="48" t="inlineStr">
+      <c r="G275" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H275" s="48" t="n"/>
-      <c r="I275" s="47" t="inlineStr">
+      <c r="H275" s="6" t="n"/>
+      <c r="I275" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J275" s="50" t="n">
+      <c r="J275" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="K275" s="50" t="n">
+      <c r="K275" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L275" s="50" t="n">
+      <c r="L275" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="M275" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N275" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O275" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P275" s="52" t="inlineStr">
+      <c r="M275" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N275" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P275" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q275" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="276">
-      <c r="A276" s="47" t="inlineStr">
+      <c r="A276" s="10" t="inlineStr">
         <is>
           <t>3.56.60.224.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B276" s="47" t="inlineStr">
+      <c r="B276" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp (TU) 24KV 22000/√3/100/√3V 15VA CCX0,5</t>
         </is>
       </c>
-      <c r="C276" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D276" s="48" t="n">
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E276" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F276" s="49" t="n">
+      <c r="E276" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F276" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G276" s="48" t="inlineStr">
+      <c r="G276" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H276" s="48" t="n"/>
-      <c r="I276" s="47" t="inlineStr">
+      <c r="H276" s="6" t="n"/>
+      <c r="I276" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J276" s="50" t="n">
+      <c r="J276" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="K276" s="50" t="n">
+      <c r="K276" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L276" s="50" t="n">
+      <c r="L276" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="M276" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N276" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O276" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P276" s="52" t="inlineStr">
+      <c r="M276" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N276" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q276" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="277">
-      <c r="A277" s="47" t="inlineStr">
+      <c r="A277" s="10" t="inlineStr">
         <is>
           <t>3.53.05.264.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B277" s="47" t="inlineStr">
+      <c r="B277" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 250/5A</t>
         </is>
       </c>
-      <c r="C277" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D277" s="48" t="n">
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E277" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F277" s="49" t="n">
+      <c r="E277" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F277" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G277" s="48" t="inlineStr">
+      <c r="G277" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H277" s="48" t="n"/>
-      <c r="I277" s="47" t="inlineStr">
+      <c r="H277" s="6" t="n"/>
+      <c r="I277" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J277" s="50" t="n">
+      <c r="J277" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="K277" s="50" t="n">
+      <c r="K277" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L277" s="50" t="n">
+      <c r="L277" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="M277" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N277" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O277" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P277" s="52" t="inlineStr">
+      <c r="M277" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q277" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="278">
-      <c r="A278" s="47" t="inlineStr">
+      <c r="A278" s="10" t="inlineStr">
         <is>
           <t>3.53.05.319.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B278" s="47" t="inlineStr">
+      <c r="B278" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 600/5A</t>
         </is>
       </c>
-      <c r="C278" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D278" s="48" t="n">
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E278" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F278" s="49" t="n">
+      <c r="E278" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F278" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G278" s="48" t="inlineStr">
+      <c r="G278" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H278" s="48" t="n"/>
-      <c r="I278" s="47" t="inlineStr">
+      <c r="H278" s="6" t="n"/>
+      <c r="I278" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J278" s="50" t="n">
+      <c r="J278" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="K278" s="50" t="n">
+      <c r="K278" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L278" s="50" t="n">
+      <c r="L278" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M278" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N278" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O278" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P278" s="52" t="inlineStr">
+      <c r="M278" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q278" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="279">
-      <c r="A279" s="47" t="inlineStr">
+      <c r="A279" s="10" t="inlineStr">
         <is>
           <t>3.53.05.330.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B279" s="47" t="inlineStr">
+      <c r="B279" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 400/5A-5VA-CCX 0,5</t>
         </is>
       </c>
-      <c r="C279" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D279" s="48" t="n">
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E279" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F279" s="49" t="n">
+      <c r="E279" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F279" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G279" s="48" t="inlineStr">
+      <c r="G279" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H279" s="48" t="n"/>
-      <c r="I279" s="47" t="inlineStr">
+      <c r="H279" s="6" t="n"/>
+      <c r="I279" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J279" s="50" t="n">
+      <c r="J279" s="43" t="n">
         <v>17</v>
       </c>
-      <c r="K279" s="50" t="n">
+      <c r="K279" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L279" s="50" t="n">
+      <c r="L279" s="43" t="n">
         <v>17</v>
       </c>
-      <c r="M279" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N279" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P279" s="52" t="inlineStr">
+      <c r="M279" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q279" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="280">
-      <c r="A280" s="47" t="inlineStr">
+      <c r="A280" s="10" t="inlineStr">
         <is>
           <t>3.53.05.203.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B280" s="47" t="inlineStr">
+      <c r="B280" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 200/5A</t>
         </is>
       </c>
-      <c r="C280" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D280" s="48" t="n">
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E280" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F280" s="49" t="n">
+      <c r="E280" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F280" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G280" s="48" t="inlineStr">
+      <c r="G280" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H280" s="48" t="n"/>
-      <c r="I280" s="47" t="inlineStr">
+      <c r="H280" s="6" t="n"/>
+      <c r="I280" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J280" s="50" t="n">
+      <c r="J280" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="K280" s="50" t="n">
+      <c r="K280" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L280" s="50" t="n">
+      <c r="L280" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M280" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N280" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O280" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P280" s="52" t="inlineStr">
+      <c r="M280" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
-        </is>
-      </c>
-      <c r="Q280" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -19080,139 +17633,124 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q281" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="282">
-      <c r="A282" s="47" t="inlineStr">
+      <c r="A282" s="10" t="inlineStr">
         <is>
           <t>3.53.05.318.VIE.00.BXX</t>
         </is>
       </c>
-      <c r="B282" s="47" t="inlineStr">
+      <c r="B282" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 500/5A</t>
         </is>
       </c>
-      <c r="C282" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D282" s="48" t="n">
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E282" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F282" s="49" t="n">
+      <c r="E282" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F282" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G282" s="48" t="inlineStr">
+      <c r="G282" s="5" t="inlineStr">
         <is>
           <t>01.VH8.12.0056</t>
         </is>
       </c>
-      <c r="H282" s="48" t="n"/>
-      <c r="I282" s="47" t="inlineStr">
+      <c r="H282" s="6" t="n"/>
+      <c r="I282" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J282" s="50" t="n">
+      <c r="J282" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="K282" s="50" t="n">
+      <c r="K282" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L282" s="50" t="n">
+      <c r="L282" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="M282" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N282" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O282" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P282" s="52" t="inlineStr">
+      <c r="M282" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q282" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
-        </is>
-      </c>
     </row>
     <row r="283">
-      <c r="A283" s="47" t="inlineStr">
+      <c r="A283" s="10" t="inlineStr">
         <is>
           <t>3.53.05.318.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B283" s="47" t="inlineStr">
+      <c r="B283" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến dòng điện (CT) 600V 500/5A</t>
         </is>
       </c>
-      <c r="C283" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D283" s="48" t="n">
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E283" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F283" s="49" t="n">
+      <c r="E283" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F283" s="4" t="n">
         <v>46155</v>
       </c>
-      <c r="G283" s="48" t="inlineStr">
+      <c r="G283" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0044</t>
         </is>
       </c>
-      <c r="H283" s="48" t="n"/>
-      <c r="I283" s="47" t="inlineStr">
+      <c r="H283" s="6" t="n"/>
+      <c r="I283" s="9" t="inlineStr">
         <is>
           <t>VTDA2606001 nhập thu hồi TU, TI Sửa chữa Lớn 2026</t>
         </is>
       </c>
-      <c r="J283" s="50" t="n">
+      <c r="J283" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="K283" s="50" t="n">
+      <c r="K283" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L283" s="50" t="n">
+      <c r="L283" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="M283" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N283" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O283" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P283" s="52" t="inlineStr">
+      <c r="M283" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N283" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
-        </is>
-      </c>
-      <c r="Q283" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -19275,74 +17813,64 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q284" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="285">
-      <c r="A285" s="47" t="inlineStr">
+      <c r="A285" s="10" t="inlineStr">
         <is>
           <t>3.56.60.016.VIE.00.CXA</t>
         </is>
       </c>
-      <c r="B285" s="47" t="inlineStr">
+      <c r="B285" s="10" t="inlineStr">
         <is>
           <t>SPC - Biến điện áp TU 12000/120V</t>
         </is>
       </c>
-      <c r="C285" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D285" s="48" t="n">
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E285" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F285" s="49" t="n">
+      <c r="E285" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F285" s="4" t="n">
         <v>46157</v>
       </c>
-      <c r="G285" s="48" t="inlineStr">
+      <c r="G285" s="5" t="inlineStr">
         <is>
           <t>01.VH4.12.0045</t>
         </is>
       </c>
-      <c r="H285" s="48" t="n"/>
-      <c r="I285" s="47" t="inlineStr">
+      <c r="H285" s="6" t="n"/>
+      <c r="I285" s="9" t="inlineStr">
         <is>
           <t>VTAD2606001 Nhập thu hồi TU SCL T5-2026</t>
         </is>
       </c>
-      <c r="J285" s="50" t="n">
+      <c r="J285" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="K285" s="50" t="n">
+      <c r="K285" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="L285" s="50" t="n">
+      <c r="L285" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="M285" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N285" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O285" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P285" s="52" t="inlineStr">
+      <c r="M285" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N285" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q285" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -19405,11 +17933,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q286" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" s="10" t="inlineStr">
@@ -19470,11 +17993,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q287" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" s="10" t="inlineStr">
@@ -19532,12 +18050,7 @@
       </c>
       <c r="P288" s="45" t="inlineStr">
         <is>
-          <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q288" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
+          <t>Hạ thế</t>
         </is>
       </c>
     </row>
@@ -19600,11 +18113,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q289" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" s="10" t="inlineStr">
@@ -19665,11 +18173,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q290" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" s="10" t="inlineStr">
@@ -19730,11 +18233,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q291" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" s="10" t="inlineStr">
@@ -19795,11 +18293,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q292" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" s="10" t="inlineStr">
@@ -19860,74 +18353,64 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q293" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="294">
-      <c r="A294" s="47" t="inlineStr">
+      <c r="A294" s="10" t="inlineStr">
         <is>
           <t>3.15.42.120.VIE.00.000</t>
         </is>
       </c>
-      <c r="B294" s="47" t="inlineStr">
+      <c r="B294" s="10" t="inlineStr">
         <is>
           <t>SPC - Cáp đồng bọc hạ thế CV 120mm2</t>
         </is>
       </c>
-      <c r="C294" s="48" t="inlineStr">
+      <c r="C294" s="3" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="D294" s="48" t="n">
+      <c r="D294" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E294" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F294" s="49" t="n">
+      <c r="E294" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F294" s="4" t="n">
         <v>46162</v>
       </c>
-      <c r="G294" s="48" t="inlineStr">
+      <c r="G294" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0050</t>
         </is>
       </c>
-      <c r="H294" s="48" t="n"/>
-      <c r="I294" s="47" t="inlineStr">
+      <c r="H294" s="6" t="n"/>
+      <c r="I294" s="9" t="inlineStr">
         <is>
           <t>24025-SX:Nhập Vtư từ Ctr 24025 đ/c SXKD cấp cho Ctr SCL TBA 2026-Cty Quang Vũ Thi công</t>
         </is>
       </c>
-      <c r="J294" s="50" t="n">
+      <c r="J294" s="43" t="n">
         <v>15.5</v>
       </c>
-      <c r="K294" s="50" t="n">
+      <c r="K294" s="43" t="n">
         <v>355200</v>
       </c>
-      <c r="L294" s="50" t="n">
+      <c r="L294" s="43" t="n">
         <v>5505600</v>
       </c>
-      <c r="M294" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N294" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O294" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P294" s="52" t="inlineStr">
+      <c r="M294" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N294" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
-        </is>
-      </c>
-      <c r="Q294" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -19990,11 +18473,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q295" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" s="10" t="inlineStr">
@@ -20055,74 +18533,64 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q296" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="297">
-      <c r="A297" s="47" t="inlineStr">
+      <c r="A297" s="10" t="inlineStr">
         <is>
           <t>3.30.92.025.VIE.00.000</t>
         </is>
       </c>
-      <c r="B297" s="47" t="inlineStr">
+      <c r="B297" s="10" t="inlineStr">
         <is>
           <t>SPC - Dây chì (FUSE LINK) 25A</t>
         </is>
       </c>
-      <c r="C297" s="48" t="inlineStr">
+      <c r="C297" s="3" t="inlineStr">
         <is>
           <t>Sợi</t>
         </is>
       </c>
-      <c r="D297" s="48" t="n">
+      <c r="D297" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E297" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F297" s="49" t="n">
+      <c r="E297" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F297" s="4" t="n">
         <v>46167</v>
       </c>
-      <c r="G297" s="48" t="inlineStr">
+      <c r="G297" s="5" t="inlineStr">
         <is>
           <t>01.VH6.11.0002</t>
         </is>
       </c>
-      <c r="H297" s="48" t="n"/>
-      <c r="I297" s="47" t="inlineStr">
+      <c r="H297" s="6" t="n"/>
+      <c r="I297" s="9" t="inlineStr">
         <is>
           <t>VTAD2606002-Nhập Vtư trả lại kho VHJ (PX 02.VH6.41.0006/24.04.26; 07.VHJ.56.0001/24.04.26)</t>
         </is>
       </c>
-      <c r="J297" s="50" t="n">
+      <c r="J297" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="K297" s="50" t="n">
+      <c r="K297" s="43" t="n">
         <v>46000</v>
       </c>
-      <c r="L297" s="50" t="n">
+      <c r="L297" s="43" t="n">
         <v>138000</v>
       </c>
-      <c r="M297" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N297" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O297" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P297" s="52" t="inlineStr">
+      <c r="M297" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N297" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P297" s="45" t="inlineStr">
         <is>
           <t>Trung thế</t>
-        </is>
-      </c>
-      <c r="Q297" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -20185,11 +18653,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q298" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" s="10" t="inlineStr">
@@ -20250,11 +18713,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q299" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" s="10" t="inlineStr">
@@ -20315,11 +18773,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q300" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" s="10" t="inlineStr">
@@ -20380,11 +18833,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q301" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" s="10" t="inlineStr">
@@ -20445,11 +18893,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q302" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" s="10" t="inlineStr">
@@ -20510,11 +18953,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q303" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" s="10" t="inlineStr">
@@ -20575,11 +19013,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q304" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" s="10" t="inlineStr">
@@ -20640,11 +19073,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q305" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" s="10" t="inlineStr">
@@ -20705,11 +19133,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q306" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" s="10" t="inlineStr">
@@ -20770,74 +19193,64 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q307" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="308">
-      <c r="A308" s="47" t="inlineStr">
+      <c r="A308" s="10" t="inlineStr">
         <is>
           <t>3.20.84.240.VIE.00.000</t>
         </is>
       </c>
-      <c r="B308" s="47" t="inlineStr">
+      <c r="B308" s="10" t="inlineStr">
         <is>
           <t>SPC - Đầu cosse ép đồng 240mm2</t>
         </is>
       </c>
-      <c r="C308" s="48" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="D308" s="48" t="n">
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E308" s="48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F308" s="49" t="n">
+      <c r="E308" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F308" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="G308" s="48" t="inlineStr">
+      <c r="G308" s="5" t="inlineStr">
         <is>
           <t>01.VH1.16.0052</t>
         </is>
       </c>
-      <c r="H308" s="48" t="n"/>
-      <c r="I308" s="47" t="inlineStr">
+      <c r="H308" s="6" t="n"/>
+      <c r="I308" s="9" t="inlineStr">
         <is>
           <t>24027-SX:Nhập Vtư từ Ctr 24027 đ/c SXKD cấp cho Ctr SCL TBA 2026-Cty Quang Vũ Thi công</t>
         </is>
       </c>
-      <c r="J308" s="50" t="n">
+      <c r="J308" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="K308" s="50" t="n">
+      <c r="K308" s="43" t="n">
         <v>131100</v>
       </c>
-      <c r="L308" s="50" t="n">
+      <c r="L308" s="43" t="n">
         <v>655500</v>
       </c>
-      <c r="M308" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N308" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O308" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P308" s="52" t="inlineStr">
+      <c r="M308" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N308" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P308" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
-        </is>
-      </c>
-      <c r="Q308" s="53" t="inlineStr">
-        <is>
-          <t>Thu hồi/Nhập kho</t>
         </is>
       </c>
     </row>
@@ -20900,11 +19313,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q309" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" s="10" t="inlineStr">
@@ -20965,11 +19373,6 @@
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="Q310" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" s="10" t="inlineStr">
@@ -21030,11 +19433,6 @@
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="Q311" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" s="10" t="inlineStr">
@@ -21093,11 +19491,6 @@
       <c r="P312" s="45" t="inlineStr">
         <is>
           <t>Hạ thế</t>
-        </is>
-      </c>
-      <c r="Q312" s="46" t="inlineStr">
-        <is>
-          <t>Xuất công trình</t>
         </is>
       </c>
     </row>
